--- a/artfynd/A 38268-2025 artfynd.xlsx
+++ b/artfynd/A 38268-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,6 +801,4472 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128439941</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>586701</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7089852</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128436169</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>586711</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7089755</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128438321</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78699</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>353</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>586605</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7090026</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128439819</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78699</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>353</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>586673</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7089842</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128438180</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>586656</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7090016</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128437589</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91519</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>586739</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7089865</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128440115</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>586688</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7089811</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128440016</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78699</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>353</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>586691</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7089809</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128439128</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80171</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>586657</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7089905</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128441773</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>586682</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7089791</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128438132</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90393</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>586666</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7089955</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128437499</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>586750</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7089835</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128437871</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78699</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>353</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>586697</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7089867</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128439671</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91519</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>586664</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7089915</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128437645</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79650</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>586746</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7089860</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128447261</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92660</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>586663</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7089829</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128439814</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79650</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>586672</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7089837</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128436765</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91323</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>586735</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7089818</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128439094</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78699</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>353</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>586622</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7089926</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128440316</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92664</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>586677</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7089793</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128438427</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>586613</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7090038</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128437989</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>586701</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7089891</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128438055</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>586682</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7089917</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128437686</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79650</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>586741</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7089870</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128438141</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>586666</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7089955</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128443168</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>586666</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7089771</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128436152</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>586699</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7089749</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128436148</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79650</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>586698</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7089750</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128439751</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79650</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>586681</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7089872</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128439799</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91519</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>586664</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7089845</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128439616</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91519</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>586660</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7089907</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128438005</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80164</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>586717</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7089885</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128437925</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92652</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>586697</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7089867</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128436482</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>586745</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7089805</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128437746</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91519</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>586698</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7089852</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128436295</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78699</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>353</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>586729</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7089765</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128436799</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>586743</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7089814</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128438053</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>586682</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7089916</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128437630</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>586750</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7089861</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128439054</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91519</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>586635</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7089949</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128446039</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78010</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>586654</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7089830</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128437765</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>586703</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7089847</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128439342</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91619</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>65</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Fläckporing</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>586657</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7089895</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128439704</v>
+      </c>
+      <c r="B46" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>586666</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7089914</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128439117</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>586650</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7089902</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128436111</v>
+      </c>
+      <c r="B48" t="n">
+        <v>92674</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>586697</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7089757</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38268-2025 artfynd.xlsx
+++ b/artfynd/A 38268-2025 artfynd.xlsx
@@ -901,32 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128436169</v>
+        <v>128438321</v>
       </c>
       <c r="B4" t="n">
-        <v>92648</v>
+        <v>78699</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586711</v>
+        <v>586605</v>
       </c>
       <c r="R4" t="n">
-        <v>7089755</v>
+        <v>7090026</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -998,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128438321</v>
+        <v>128436169</v>
       </c>
       <c r="B5" t="n">
-        <v>78699</v>
+        <v>92650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586605</v>
+        <v>586711</v>
       </c>
       <c r="R5" t="n">
-        <v>7090026</v>
+        <v>7089755</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1289,32 +1289,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128437589</v>
+        <v>128440016</v>
       </c>
       <c r="B8" t="n">
-        <v>91519</v>
+        <v>78699</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586739</v>
+        <v>586691</v>
       </c>
       <c r="R8" t="n">
-        <v>7089865</v>
+        <v>7089809</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1386,32 +1386,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128440115</v>
+        <v>128437589</v>
       </c>
       <c r="B9" t="n">
-        <v>92648</v>
+        <v>91521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586688</v>
+        <v>586739</v>
       </c>
       <c r="R9" t="n">
-        <v>7089811</v>
+        <v>7089865</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1483,32 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128440016</v>
+        <v>128440115</v>
       </c>
       <c r="B10" t="n">
-        <v>78699</v>
+        <v>92650</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586691</v>
+        <v>586688</v>
       </c>
       <c r="R10" t="n">
-        <v>7089809</v>
+        <v>7089811</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1580,32 +1580,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128439128</v>
+        <v>128438132</v>
       </c>
       <c r="B11" t="n">
-        <v>80171</v>
+        <v>90393</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586657</v>
+        <v>586666</v>
       </c>
       <c r="R11" t="n">
-        <v>7089905</v>
+        <v>7089955</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1680,7 +1680,7 @@
         <v>128441773</v>
       </c>
       <c r="B12" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1774,32 +1774,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128438132</v>
+        <v>128439128</v>
       </c>
       <c r="B13" t="n">
-        <v>90393</v>
+        <v>80171</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586666</v>
+        <v>586657</v>
       </c>
       <c r="R13" t="n">
-        <v>7089955</v>
+        <v>7089905</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1874,7 +1874,7 @@
         <v>128437499</v>
       </c>
       <c r="B14" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128437871</v>
+        <v>128439671</v>
       </c>
       <c r="B15" t="n">
-        <v>78699</v>
+        <v>91521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586697</v>
+        <v>586664</v>
       </c>
       <c r="R15" t="n">
-        <v>7089867</v>
+        <v>7089915</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2065,32 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128439671</v>
+        <v>128437871</v>
       </c>
       <c r="B16" t="n">
-        <v>91519</v>
+        <v>78699</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586664</v>
+        <v>586697</v>
       </c>
       <c r="R16" t="n">
-        <v>7089915</v>
+        <v>7089867</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2162,32 +2162,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128437645</v>
+        <v>128447261</v>
       </c>
       <c r="B17" t="n">
-        <v>79650</v>
+        <v>92662</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586746</v>
+        <v>586663</v>
       </c>
       <c r="R17" t="n">
-        <v>7089860</v>
+        <v>7089829</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2259,32 +2259,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128447261</v>
+        <v>128437645</v>
       </c>
       <c r="B18" t="n">
-        <v>92660</v>
+        <v>79650</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586663</v>
+        <v>586746</v>
       </c>
       <c r="R18" t="n">
-        <v>7089829</v>
+        <v>7089860</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2453,32 +2453,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128436765</v>
+        <v>128439094</v>
       </c>
       <c r="B20" t="n">
-        <v>91323</v>
+        <v>78699</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586735</v>
+        <v>586622</v>
       </c>
       <c r="R20" t="n">
-        <v>7089818</v>
+        <v>7089926</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2550,32 +2550,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128439094</v>
+        <v>128436765</v>
       </c>
       <c r="B21" t="n">
-        <v>78699</v>
+        <v>91325</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586622</v>
+        <v>586735</v>
       </c>
       <c r="R21" t="n">
-        <v>7089926</v>
+        <v>7089818</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2647,10 +2647,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128440316</v>
+        <v>128438427</v>
       </c>
       <c r="B22" t="n">
-        <v>92664</v>
+        <v>92843</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2658,21 +2658,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2059</v>
+        <v>2079</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586677</v>
+        <v>586613</v>
       </c>
       <c r="R22" t="n">
-        <v>7089793</v>
+        <v>7090038</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2744,10 +2744,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128438427</v>
+        <v>128440316</v>
       </c>
       <c r="B23" t="n">
-        <v>92841</v>
+        <v>92666</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2755,21 +2755,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2079</v>
+        <v>2059</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586613</v>
+        <v>586677</v>
       </c>
       <c r="R23" t="n">
-        <v>7090038</v>
+        <v>7089793</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2841,32 +2841,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128437989</v>
+        <v>128438055</v>
       </c>
       <c r="B24" t="n">
-        <v>80135</v>
+        <v>92650</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586701</v>
+        <v>586682</v>
       </c>
       <c r="R24" t="n">
-        <v>7089891</v>
+        <v>7089917</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2938,32 +2938,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128438055</v>
+        <v>128437989</v>
       </c>
       <c r="B25" t="n">
-        <v>92648</v>
+        <v>80135</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586682</v>
+        <v>586701</v>
       </c>
       <c r="R25" t="n">
-        <v>7089917</v>
+        <v>7089891</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3035,10 +3035,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128437686</v>
+        <v>128438141</v>
       </c>
       <c r="B26" t="n">
-        <v>79650</v>
+        <v>80135</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3046,21 +3046,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586741</v>
+        <v>586666</v>
       </c>
       <c r="R26" t="n">
-        <v>7089870</v>
+        <v>7089955</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128438141</v>
+        <v>128437686</v>
       </c>
       <c r="B27" t="n">
-        <v>80135</v>
+        <v>79650</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3143,21 +3143,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3167,10 +3167,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586666</v>
+        <v>586741</v>
       </c>
       <c r="R27" t="n">
-        <v>7089955</v>
+        <v>7089870</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3232,7 +3232,7 @@
         <v>128443168</v>
       </c>
       <c r="B28" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3326,32 +3326,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128436152</v>
+        <v>128439799</v>
       </c>
       <c r="B29" t="n">
-        <v>79032</v>
+        <v>91521</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586699</v>
+        <v>586664</v>
       </c>
       <c r="R29" t="n">
-        <v>7089749</v>
+        <v>7089845</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3423,32 +3423,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128436148</v>
+        <v>128439616</v>
       </c>
       <c r="B30" t="n">
-        <v>79650</v>
+        <v>91521</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>586698</v>
+        <v>586660</v>
       </c>
       <c r="R30" t="n">
-        <v>7089750</v>
+        <v>7089907</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3617,32 +3617,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128439799</v>
+        <v>128436152</v>
       </c>
       <c r="B32" t="n">
-        <v>91519</v>
+        <v>79032</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586664</v>
+        <v>586699</v>
       </c>
       <c r="R32" t="n">
-        <v>7089845</v>
+        <v>7089749</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3714,32 +3714,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128439616</v>
+        <v>128438005</v>
       </c>
       <c r="B33" t="n">
-        <v>91519</v>
+        <v>80164</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1503</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586660</v>
+        <v>586717</v>
       </c>
       <c r="R33" t="n">
-        <v>7089907</v>
+        <v>7089885</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3811,32 +3811,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128438005</v>
+        <v>128436148</v>
       </c>
       <c r="B34" t="n">
-        <v>80164</v>
+        <v>79650</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586717</v>
+        <v>586698</v>
       </c>
       <c r="R34" t="n">
-        <v>7089885</v>
+        <v>7089750</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3911,7 +3911,7 @@
         <v>128437925</v>
       </c>
       <c r="B35" t="n">
-        <v>92652</v>
+        <v>92654</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4102,32 +4102,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128437746</v>
+        <v>128436295</v>
       </c>
       <c r="B37" t="n">
-        <v>91519</v>
+        <v>78699</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586698</v>
+        <v>586729</v>
       </c>
       <c r="R37" t="n">
-        <v>7089852</v>
+        <v>7089765</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4199,32 +4199,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128436295</v>
+        <v>128437746</v>
       </c>
       <c r="B38" t="n">
-        <v>78699</v>
+        <v>91521</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586729</v>
+        <v>586698</v>
       </c>
       <c r="R38" t="n">
-        <v>7089765</v>
+        <v>7089852</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4490,32 +4490,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128437630</v>
+        <v>128439054</v>
       </c>
       <c r="B41" t="n">
-        <v>78790</v>
+        <v>91521</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586750</v>
+        <v>586635</v>
       </c>
       <c r="R41" t="n">
-        <v>7089861</v>
+        <v>7089949</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4587,32 +4587,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128439054</v>
+        <v>128437630</v>
       </c>
       <c r="B42" t="n">
-        <v>91519</v>
+        <v>78790</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586635</v>
+        <v>586750</v>
       </c>
       <c r="R42" t="n">
-        <v>7089949</v>
+        <v>7089861</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4781,32 +4781,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128437765</v>
+        <v>128439342</v>
       </c>
       <c r="B44" t="n">
-        <v>79032</v>
+        <v>91621</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4816,10 +4816,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586703</v>
+        <v>586657</v>
       </c>
       <c r="R44" t="n">
-        <v>7089847</v>
+        <v>7089895</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4878,32 +4878,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128439342</v>
+        <v>128439704</v>
       </c>
       <c r="B45" t="n">
-        <v>91619</v>
+        <v>92843</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586657</v>
+        <v>586666</v>
       </c>
       <c r="R45" t="n">
-        <v>7089895</v>
+        <v>7089914</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -4975,10 +4975,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128439704</v>
+        <v>128437765</v>
       </c>
       <c r="B46" t="n">
-        <v>92841</v>
+        <v>79032</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4986,21 +4986,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586666</v>
+        <v>586703</v>
       </c>
       <c r="R46" t="n">
-        <v>7089914</v>
+        <v>7089847</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5172,7 +5172,7 @@
         <v>128436111</v>
       </c>
       <c r="B48" t="n">
-        <v>92674</v>
+        <v>92676</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 38268-2025 artfynd.xlsx
+++ b/artfynd/A 38268-2025 artfynd.xlsx
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128439819</v>
+        <v>128438180</v>
       </c>
       <c r="B6" t="n">
-        <v>78699</v>
+        <v>80135</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586673</v>
+        <v>586656</v>
       </c>
       <c r="R6" t="n">
-        <v>7089842</v>
+        <v>7090016</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128438180</v>
+        <v>128439819</v>
       </c>
       <c r="B7" t="n">
-        <v>80135</v>
+        <v>78699</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,21 +1203,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586656</v>
+        <v>586673</v>
       </c>
       <c r="R7" t="n">
-        <v>7090016</v>
+        <v>7089842</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -4296,10 +4296,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128436799</v>
+        <v>128438053</v>
       </c>
       <c r="B39" t="n">
-        <v>79032</v>
+        <v>78790</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4307,21 +4307,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586743</v>
+        <v>586682</v>
       </c>
       <c r="R39" t="n">
-        <v>7089814</v>
+        <v>7089916</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128438053</v>
+        <v>128436799</v>
       </c>
       <c r="B40" t="n">
-        <v>78790</v>
+        <v>79032</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4404,21 +4404,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586682</v>
+        <v>586743</v>
       </c>
       <c r="R40" t="n">
-        <v>7089916</v>
+        <v>7089814</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>

--- a/artfynd/A 38268-2025 artfynd.xlsx
+++ b/artfynd/A 38268-2025 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128439941</v>
       </c>
       <c r="B3" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>128438321</v>
       </c>
       <c r="B4" t="n">
-        <v>78699</v>
+        <v>78749</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128436169</v>
       </c>
       <c r="B5" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128438180</v>
+        <v>128439819</v>
       </c>
       <c r="B6" t="n">
-        <v>80135</v>
+        <v>78749</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586656</v>
+        <v>586673</v>
       </c>
       <c r="R6" t="n">
-        <v>7090016</v>
+        <v>7089842</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128439819</v>
+        <v>128438180</v>
       </c>
       <c r="B7" t="n">
-        <v>78699</v>
+        <v>80188</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,21 +1203,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586673</v>
+        <v>586656</v>
       </c>
       <c r="R7" t="n">
-        <v>7089842</v>
+        <v>7090016</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1289,32 +1289,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128440016</v>
+        <v>128437589</v>
       </c>
       <c r="B8" t="n">
-        <v>78699</v>
+        <v>91613</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586691</v>
+        <v>586739</v>
       </c>
       <c r="R8" t="n">
-        <v>7089809</v>
+        <v>7089865</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1386,32 +1386,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128437589</v>
+        <v>128440016</v>
       </c>
       <c r="B9" t="n">
-        <v>91521</v>
+        <v>78749</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586739</v>
+        <v>586691</v>
       </c>
       <c r="R9" t="n">
-        <v>7089865</v>
+        <v>7089809</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1486,7 +1486,7 @@
         <v>128440115</v>
       </c>
       <c r="B10" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>128438132</v>
       </c>
       <c r="B11" t="n">
-        <v>90393</v>
+        <v>90485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>128441773</v>
       </c>
       <c r="B12" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>128439128</v>
       </c>
       <c r="B13" t="n">
-        <v>80171</v>
+        <v>80224</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128437499</v>
+        <v>128437871</v>
       </c>
       <c r="B14" t="n">
-        <v>92650</v>
+        <v>78749</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586750</v>
+        <v>586697</v>
       </c>
       <c r="R14" t="n">
-        <v>7089835</v>
+        <v>7089867</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128439671</v>
+        <v>128437499</v>
       </c>
       <c r="B15" t="n">
-        <v>91521</v>
+        <v>92742</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586664</v>
+        <v>586750</v>
       </c>
       <c r="R15" t="n">
-        <v>7089915</v>
+        <v>7089835</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2065,32 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128437871</v>
+        <v>128439671</v>
       </c>
       <c r="B16" t="n">
-        <v>78699</v>
+        <v>91613</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586697</v>
+        <v>586664</v>
       </c>
       <c r="R16" t="n">
-        <v>7089867</v>
+        <v>7089915</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2165,7 +2165,7 @@
         <v>128447261</v>
       </c>
       <c r="B17" t="n">
-        <v>92662</v>
+        <v>92754</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>128437645</v>
       </c>
       <c r="B18" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>128439814</v>
       </c>
       <c r="B19" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128439094</v>
       </c>
       <c r="B20" t="n">
-        <v>78699</v>
+        <v>78749</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>128436765</v>
       </c>
       <c r="B21" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>128438427</v>
       </c>
       <c r="B22" t="n">
-        <v>92843</v>
+        <v>92935</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>128440316</v>
       </c>
       <c r="B23" t="n">
-        <v>92666</v>
+        <v>92758</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2841,32 +2841,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128438055</v>
+        <v>128437989</v>
       </c>
       <c r="B24" t="n">
-        <v>92650</v>
+        <v>80188</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586682</v>
+        <v>586701</v>
       </c>
       <c r="R24" t="n">
-        <v>7089917</v>
+        <v>7089891</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2938,32 +2938,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128437989</v>
+        <v>128438055</v>
       </c>
       <c r="B25" t="n">
-        <v>80135</v>
+        <v>92742</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586701</v>
+        <v>586682</v>
       </c>
       <c r="R25" t="n">
-        <v>7089891</v>
+        <v>7089917</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3038,7 +3038,7 @@
         <v>128438141</v>
       </c>
       <c r="B26" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>128437686</v>
       </c>
       <c r="B27" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>128443168</v>
       </c>
       <c r="B28" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>128439799</v>
       </c>
       <c r="B29" t="n">
-        <v>91521</v>
+        <v>91613</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>128439616</v>
       </c>
       <c r="B30" t="n">
-        <v>91521</v>
+        <v>91613</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>128439751</v>
       </c>
       <c r="B31" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3617,32 +3617,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128436152</v>
+        <v>128438005</v>
       </c>
       <c r="B32" t="n">
-        <v>79032</v>
+        <v>80217</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586699</v>
+        <v>586717</v>
       </c>
       <c r="R32" t="n">
-        <v>7089749</v>
+        <v>7089885</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3714,32 +3714,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128438005</v>
+        <v>128436148</v>
       </c>
       <c r="B33" t="n">
-        <v>80164</v>
+        <v>79702</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586717</v>
+        <v>586698</v>
       </c>
       <c r="R33" t="n">
-        <v>7089885</v>
+        <v>7089750</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128436148</v>
+        <v>128436152</v>
       </c>
       <c r="B34" t="n">
-        <v>79650</v>
+        <v>79083</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3822,21 +3822,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586698</v>
+        <v>586699</v>
       </c>
       <c r="R34" t="n">
-        <v>7089750</v>
+        <v>7089749</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3911,7 +3911,7 @@
         <v>128437925</v>
       </c>
       <c r="B35" t="n">
-        <v>92654</v>
+        <v>92746</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>128436482</v>
       </c>
       <c r="B36" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>128436295</v>
       </c>
       <c r="B37" t="n">
-        <v>78699</v>
+        <v>78749</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>128437746</v>
       </c>
       <c r="B38" t="n">
-        <v>91521</v>
+        <v>91613</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4296,10 +4296,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128438053</v>
+        <v>128436799</v>
       </c>
       <c r="B39" t="n">
-        <v>78790</v>
+        <v>79083</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4307,21 +4307,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586682</v>
+        <v>586743</v>
       </c>
       <c r="R39" t="n">
-        <v>7089916</v>
+        <v>7089814</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128436799</v>
+        <v>128438053</v>
       </c>
       <c r="B40" t="n">
-        <v>79032</v>
+        <v>78840</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4404,21 +4404,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586743</v>
+        <v>586682</v>
       </c>
       <c r="R40" t="n">
-        <v>7089814</v>
+        <v>7089916</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4493,7 +4493,7 @@
         <v>128439054</v>
       </c>
       <c r="B41" t="n">
-        <v>91521</v>
+        <v>91613</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4587,10 +4587,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128437630</v>
+        <v>128446039</v>
       </c>
       <c r="B42" t="n">
-        <v>78790</v>
+        <v>78055</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4598,21 +4598,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586750</v>
+        <v>586654</v>
       </c>
       <c r="R42" t="n">
-        <v>7089861</v>
+        <v>7089830</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4684,10 +4684,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128446039</v>
+        <v>128437630</v>
       </c>
       <c r="B43" t="n">
-        <v>78010</v>
+        <v>78840</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4695,21 +4695,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586654</v>
+        <v>586750</v>
       </c>
       <c r="R43" t="n">
-        <v>7089830</v>
+        <v>7089861</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4781,32 +4781,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128439342</v>
+        <v>128439117</v>
       </c>
       <c r="B44" t="n">
-        <v>91621</v>
+        <v>80188</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>65</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4816,10 +4816,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586657</v>
+        <v>586650</v>
       </c>
       <c r="R44" t="n">
-        <v>7089895</v>
+        <v>7089902</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4878,32 +4878,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128439704</v>
+        <v>128439342</v>
       </c>
       <c r="B45" t="n">
-        <v>92843</v>
+        <v>91713</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2079</v>
+        <v>65</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586666</v>
+        <v>586657</v>
       </c>
       <c r="R45" t="n">
-        <v>7089914</v>
+        <v>7089895</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -4975,10 +4975,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128437765</v>
+        <v>128439704</v>
       </c>
       <c r="B46" t="n">
-        <v>79032</v>
+        <v>92935</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4986,21 +4986,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586703</v>
+        <v>586666</v>
       </c>
       <c r="R46" t="n">
-        <v>7089847</v>
+        <v>7089914</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5072,10 +5072,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128439117</v>
+        <v>128437765</v>
       </c>
       <c r="B47" t="n">
-        <v>80135</v>
+        <v>79083</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5083,21 +5083,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586650</v>
+        <v>586703</v>
       </c>
       <c r="R47" t="n">
-        <v>7089902</v>
+        <v>7089847</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>

--- a/artfynd/A 38268-2025 artfynd.xlsx
+++ b/artfynd/A 38268-2025 artfynd.xlsx
@@ -901,32 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128438321</v>
+        <v>128436169</v>
       </c>
       <c r="B4" t="n">
-        <v>78749</v>
+        <v>92742</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586605</v>
+        <v>586711</v>
       </c>
       <c r="R4" t="n">
-        <v>7090026</v>
+        <v>7089755</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -998,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128436169</v>
+        <v>128438321</v>
       </c>
       <c r="B5" t="n">
-        <v>92742</v>
+        <v>78749</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586711</v>
+        <v>586605</v>
       </c>
       <c r="R5" t="n">
-        <v>7089755</v>
+        <v>7090026</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1289,32 +1289,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128437589</v>
+        <v>128440016</v>
       </c>
       <c r="B8" t="n">
-        <v>91613</v>
+        <v>78749</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586739</v>
+        <v>586691</v>
       </c>
       <c r="R8" t="n">
-        <v>7089865</v>
+        <v>7089809</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1386,32 +1386,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128440016</v>
+        <v>128437589</v>
       </c>
       <c r="B9" t="n">
-        <v>78749</v>
+        <v>91613</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586691</v>
+        <v>586739</v>
       </c>
       <c r="R9" t="n">
-        <v>7089809</v>
+        <v>7089865</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1677,10 +1677,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128441773</v>
+        <v>128439128</v>
       </c>
       <c r="B12" t="n">
-        <v>92742</v>
+        <v>80224</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1688,21 +1688,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586682</v>
+        <v>586657</v>
       </c>
       <c r="R12" t="n">
-        <v>7089791</v>
+        <v>7089905</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1774,10 +1774,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128439128</v>
+        <v>128441773</v>
       </c>
       <c r="B13" t="n">
-        <v>80224</v>
+        <v>92742</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1785,21 +1785,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586657</v>
+        <v>586682</v>
       </c>
       <c r="R13" t="n">
-        <v>7089905</v>
+        <v>7089791</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128437499</v>
+        <v>128439671</v>
       </c>
       <c r="B15" t="n">
-        <v>92742</v>
+        <v>91613</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586750</v>
+        <v>586664</v>
       </c>
       <c r="R15" t="n">
-        <v>7089835</v>
+        <v>7089915</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2065,32 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128439671</v>
+        <v>128437499</v>
       </c>
       <c r="B16" t="n">
-        <v>91613</v>
+        <v>92742</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586664</v>
+        <v>586750</v>
       </c>
       <c r="R16" t="n">
-        <v>7089915</v>
+        <v>7089835</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2162,32 +2162,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128447261</v>
+        <v>128437645</v>
       </c>
       <c r="B17" t="n">
-        <v>92754</v>
+        <v>79702</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586663</v>
+        <v>586746</v>
       </c>
       <c r="R17" t="n">
-        <v>7089829</v>
+        <v>7089860</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2259,32 +2259,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128437645</v>
+        <v>128447261</v>
       </c>
       <c r="B18" t="n">
-        <v>79702</v>
+        <v>92754</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586746</v>
+        <v>586663</v>
       </c>
       <c r="R18" t="n">
-        <v>7089860</v>
+        <v>7089829</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -3035,32 +3035,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128438141</v>
+        <v>128443168</v>
       </c>
       <c r="B26" t="n">
-        <v>80188</v>
+        <v>92742</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,7 +3073,7 @@
         <v>586666</v>
       </c>
       <c r="R26" t="n">
-        <v>7089955</v>
+        <v>7089771</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128437686</v>
+        <v>128438141</v>
       </c>
       <c r="B27" t="n">
-        <v>79702</v>
+        <v>80188</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3143,21 +3143,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3167,10 +3167,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586741</v>
+        <v>586666</v>
       </c>
       <c r="R27" t="n">
-        <v>7089870</v>
+        <v>7089955</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3229,32 +3229,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128443168</v>
+        <v>128437686</v>
       </c>
       <c r="B28" t="n">
-        <v>92742</v>
+        <v>79702</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586666</v>
+        <v>586741</v>
       </c>
       <c r="R28" t="n">
-        <v>7089771</v>
+        <v>7089870</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3617,32 +3617,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128438005</v>
+        <v>128436152</v>
       </c>
       <c r="B32" t="n">
-        <v>80217</v>
+        <v>79083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586717</v>
+        <v>586699</v>
       </c>
       <c r="R32" t="n">
-        <v>7089885</v>
+        <v>7089749</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3714,32 +3714,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128436148</v>
+        <v>128438005</v>
       </c>
       <c r="B33" t="n">
-        <v>79702</v>
+        <v>80217</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586698</v>
+        <v>586717</v>
       </c>
       <c r="R33" t="n">
-        <v>7089750</v>
+        <v>7089885</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128436152</v>
+        <v>128436148</v>
       </c>
       <c r="B34" t="n">
-        <v>79083</v>
+        <v>79702</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3822,21 +3822,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586699</v>
+        <v>586698</v>
       </c>
       <c r="R34" t="n">
-        <v>7089749</v>
+        <v>7089750</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4102,32 +4102,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128436295</v>
+        <v>128437746</v>
       </c>
       <c r="B37" t="n">
-        <v>78749</v>
+        <v>91613</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586729</v>
+        <v>586698</v>
       </c>
       <c r="R37" t="n">
-        <v>7089765</v>
+        <v>7089852</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4199,32 +4199,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128437746</v>
+        <v>128436799</v>
       </c>
       <c r="B38" t="n">
-        <v>91613</v>
+        <v>79083</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586698</v>
+        <v>586743</v>
       </c>
       <c r="R38" t="n">
-        <v>7089852</v>
+        <v>7089814</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4296,10 +4296,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128436799</v>
+        <v>128438053</v>
       </c>
       <c r="B39" t="n">
-        <v>79083</v>
+        <v>78840</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4307,21 +4307,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586743</v>
+        <v>586682</v>
       </c>
       <c r="R39" t="n">
-        <v>7089814</v>
+        <v>7089916</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128438053</v>
+        <v>128436295</v>
       </c>
       <c r="B40" t="n">
-        <v>78840</v>
+        <v>78749</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4404,21 +4404,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586682</v>
+        <v>586729</v>
       </c>
       <c r="R40" t="n">
-        <v>7089916</v>
+        <v>7089765</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4490,32 +4490,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128439054</v>
+        <v>128437630</v>
       </c>
       <c r="B41" t="n">
-        <v>91613</v>
+        <v>78840</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586635</v>
+        <v>586750</v>
       </c>
       <c r="R41" t="n">
-        <v>7089949</v>
+        <v>7089861</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4684,32 +4684,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128437630</v>
+        <v>128439054</v>
       </c>
       <c r="B43" t="n">
-        <v>78840</v>
+        <v>91613</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586750</v>
+        <v>586635</v>
       </c>
       <c r="R43" t="n">
-        <v>7089861</v>
+        <v>7089949</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4781,10 +4781,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128439117</v>
+        <v>128437765</v>
       </c>
       <c r="B44" t="n">
-        <v>80188</v>
+        <v>79083</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4792,21 +4792,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4816,10 +4816,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586650</v>
+        <v>586703</v>
       </c>
       <c r="R44" t="n">
-        <v>7089902</v>
+        <v>7089847</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4878,32 +4878,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128439342</v>
+        <v>128439117</v>
       </c>
       <c r="B45" t="n">
-        <v>91713</v>
+        <v>80188</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>65</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586657</v>
+        <v>586650</v>
       </c>
       <c r="R45" t="n">
-        <v>7089895</v>
+        <v>7089902</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -4975,32 +4975,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128439704</v>
+        <v>128439342</v>
       </c>
       <c r="B46" t="n">
-        <v>92935</v>
+        <v>91713</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2079</v>
+        <v>65</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586666</v>
+        <v>586657</v>
       </c>
       <c r="R46" t="n">
-        <v>7089914</v>
+        <v>7089895</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5072,10 +5072,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128437765</v>
+        <v>128439704</v>
       </c>
       <c r="B47" t="n">
-        <v>79083</v>
+        <v>92935</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5083,21 +5083,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586703</v>
+        <v>586666</v>
       </c>
       <c r="R47" t="n">
-        <v>7089847</v>
+        <v>7089914</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5172,7 +5172,7 @@
         <v>128436111</v>
       </c>
       <c r="B48" t="n">
-        <v>92676</v>
+        <v>92768</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 38268-2025 artfynd.xlsx
+++ b/artfynd/A 38268-2025 artfynd.xlsx
@@ -2841,32 +2841,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128437989</v>
+        <v>128438055</v>
       </c>
       <c r="B24" t="n">
-        <v>80188</v>
+        <v>92742</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586701</v>
+        <v>586682</v>
       </c>
       <c r="R24" t="n">
-        <v>7089891</v>
+        <v>7089917</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2938,32 +2938,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128438055</v>
+        <v>128437989</v>
       </c>
       <c r="B25" t="n">
-        <v>92742</v>
+        <v>80188</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586682</v>
+        <v>586701</v>
       </c>
       <c r="R25" t="n">
-        <v>7089917</v>
+        <v>7089891</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -4102,32 +4102,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128437746</v>
+        <v>128436295</v>
       </c>
       <c r="B37" t="n">
-        <v>91613</v>
+        <v>78749</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586698</v>
+        <v>586729</v>
       </c>
       <c r="R37" t="n">
-        <v>7089852</v>
+        <v>7089765</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4199,32 +4199,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128436799</v>
+        <v>128437746</v>
       </c>
       <c r="B38" t="n">
-        <v>79083</v>
+        <v>91613</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586743</v>
+        <v>586698</v>
       </c>
       <c r="R38" t="n">
-        <v>7089814</v>
+        <v>7089852</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4296,10 +4296,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128438053</v>
+        <v>128436799</v>
       </c>
       <c r="B39" t="n">
-        <v>78840</v>
+        <v>79083</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4307,21 +4307,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586682</v>
+        <v>586743</v>
       </c>
       <c r="R39" t="n">
-        <v>7089916</v>
+        <v>7089814</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128436295</v>
+        <v>128438053</v>
       </c>
       <c r="B40" t="n">
-        <v>78749</v>
+        <v>78840</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4404,21 +4404,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586729</v>
+        <v>586682</v>
       </c>
       <c r="R40" t="n">
-        <v>7089765</v>
+        <v>7089916</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4490,32 +4490,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128437630</v>
+        <v>128439054</v>
       </c>
       <c r="B41" t="n">
-        <v>78840</v>
+        <v>91613</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586750</v>
+        <v>586635</v>
       </c>
       <c r="R41" t="n">
-        <v>7089861</v>
+        <v>7089949</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4587,10 +4587,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128446039</v>
+        <v>128437630</v>
       </c>
       <c r="B42" t="n">
-        <v>78055</v>
+        <v>78840</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4598,21 +4598,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586654</v>
+        <v>586750</v>
       </c>
       <c r="R42" t="n">
-        <v>7089830</v>
+        <v>7089861</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4684,32 +4684,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128439054</v>
+        <v>128446039</v>
       </c>
       <c r="B43" t="n">
-        <v>91613</v>
+        <v>78055</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1503</v>
+        <v>6487</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586635</v>
+        <v>586654</v>
       </c>
       <c r="R43" t="n">
-        <v>7089949</v>
+        <v>7089830</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4781,32 +4781,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128437765</v>
+        <v>128439342</v>
       </c>
       <c r="B44" t="n">
-        <v>79083</v>
+        <v>91713</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4816,10 +4816,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586703</v>
+        <v>586657</v>
       </c>
       <c r="R44" t="n">
-        <v>7089847</v>
+        <v>7089895</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4878,10 +4878,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128439117</v>
+        <v>128439704</v>
       </c>
       <c r="B45" t="n">
-        <v>80188</v>
+        <v>92935</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4889,21 +4889,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586650</v>
+        <v>586666</v>
       </c>
       <c r="R45" t="n">
-        <v>7089902</v>
+        <v>7089914</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -4975,32 +4975,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128439342</v>
+        <v>128437765</v>
       </c>
       <c r="B46" t="n">
-        <v>91713</v>
+        <v>79083</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586657</v>
+        <v>586703</v>
       </c>
       <c r="R46" t="n">
-        <v>7089895</v>
+        <v>7089847</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5072,10 +5072,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128439704</v>
+        <v>128439117</v>
       </c>
       <c r="B47" t="n">
-        <v>92935</v>
+        <v>80188</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5083,21 +5083,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586666</v>
+        <v>586650</v>
       </c>
       <c r="R47" t="n">
-        <v>7089914</v>
+        <v>7089902</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>

--- a/artfynd/A 38268-2025 artfynd.xlsx
+++ b/artfynd/A 38268-2025 artfynd.xlsx
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128439819</v>
+        <v>128438180</v>
       </c>
       <c r="B6" t="n">
-        <v>78749</v>
+        <v>80188</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586673</v>
+        <v>586656</v>
       </c>
       <c r="R6" t="n">
-        <v>7089842</v>
+        <v>7090016</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128438180</v>
+        <v>128439819</v>
       </c>
       <c r="B7" t="n">
-        <v>80188</v>
+        <v>78749</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,21 +1203,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586656</v>
+        <v>586673</v>
       </c>
       <c r="R7" t="n">
-        <v>7090016</v>
+        <v>7089842</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -3035,32 +3035,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128443168</v>
+        <v>128438141</v>
       </c>
       <c r="B26" t="n">
-        <v>92742</v>
+        <v>80188</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,7 +3073,7 @@
         <v>586666</v>
       </c>
       <c r="R26" t="n">
-        <v>7089771</v>
+        <v>7089955</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128438141</v>
+        <v>128437686</v>
       </c>
       <c r="B27" t="n">
-        <v>80188</v>
+        <v>79702</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3143,21 +3143,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3167,10 +3167,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586666</v>
+        <v>586741</v>
       </c>
       <c r="R27" t="n">
-        <v>7089955</v>
+        <v>7089870</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3229,32 +3229,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128437686</v>
+        <v>128443168</v>
       </c>
       <c r="B28" t="n">
-        <v>79702</v>
+        <v>92742</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586741</v>
+        <v>586666</v>
       </c>
       <c r="R28" t="n">
-        <v>7089870</v>
+        <v>7089771</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -5172,7 +5172,7 @@
         <v>128436111</v>
       </c>
       <c r="B48" t="n">
-        <v>92768</v>
+        <v>92774</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 38268-2025 artfynd.xlsx
+++ b/artfynd/A 38268-2025 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128439941</v>
       </c>
       <c r="B3" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>128436169</v>
       </c>
       <c r="B4" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128438321</v>
       </c>
       <c r="B5" t="n">
-        <v>78749</v>
+        <v>78753</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128438180</v>
+        <v>128439819</v>
       </c>
       <c r="B6" t="n">
-        <v>80188</v>
+        <v>78753</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586656</v>
+        <v>586673</v>
       </c>
       <c r="R6" t="n">
-        <v>7090016</v>
+        <v>7089842</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128439819</v>
+        <v>128438180</v>
       </c>
       <c r="B7" t="n">
-        <v>78749</v>
+        <v>80192</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,21 +1203,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586673</v>
+        <v>586656</v>
       </c>
       <c r="R7" t="n">
-        <v>7089842</v>
+        <v>7090016</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1289,32 +1289,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128440016</v>
+        <v>128440115</v>
       </c>
       <c r="B8" t="n">
-        <v>78749</v>
+        <v>92754</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586691</v>
+        <v>586688</v>
       </c>
       <c r="R8" t="n">
-        <v>7089809</v>
+        <v>7089811</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1386,32 +1386,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128437589</v>
+        <v>128440016</v>
       </c>
       <c r="B9" t="n">
-        <v>91613</v>
+        <v>78753</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586739</v>
+        <v>586691</v>
       </c>
       <c r="R9" t="n">
-        <v>7089865</v>
+        <v>7089809</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1483,32 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128440115</v>
+        <v>128437589</v>
       </c>
       <c r="B10" t="n">
-        <v>92742</v>
+        <v>91625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586688</v>
+        <v>586739</v>
       </c>
       <c r="R10" t="n">
-        <v>7089811</v>
+        <v>7089865</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1580,32 +1580,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128438132</v>
+        <v>128441773</v>
       </c>
       <c r="B11" t="n">
-        <v>90485</v>
+        <v>92754</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586666</v>
+        <v>586682</v>
       </c>
       <c r="R11" t="n">
-        <v>7089955</v>
+        <v>7089791</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1677,32 +1677,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128439128</v>
+        <v>128438132</v>
       </c>
       <c r="B12" t="n">
-        <v>80224</v>
+        <v>90497</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586657</v>
+        <v>586666</v>
       </c>
       <c r="R12" t="n">
-        <v>7089905</v>
+        <v>7089955</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1774,10 +1774,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128441773</v>
+        <v>128439128</v>
       </c>
       <c r="B13" t="n">
-        <v>92742</v>
+        <v>80228</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1785,21 +1785,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586682</v>
+        <v>586657</v>
       </c>
       <c r="R13" t="n">
-        <v>7089791</v>
+        <v>7089905</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128437871</v>
+        <v>128437499</v>
       </c>
       <c r="B14" t="n">
-        <v>78749</v>
+        <v>92754</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586697</v>
+        <v>586750</v>
       </c>
       <c r="R14" t="n">
-        <v>7089867</v>
+        <v>7089835</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1971,7 +1971,7 @@
         <v>128439671</v>
       </c>
       <c r="B15" t="n">
-        <v>91613</v>
+        <v>91625</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,32 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128437499</v>
+        <v>128437871</v>
       </c>
       <c r="B16" t="n">
-        <v>92742</v>
+        <v>78753</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586750</v>
+        <v>586697</v>
       </c>
       <c r="R16" t="n">
-        <v>7089835</v>
+        <v>7089867</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2162,32 +2162,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128437645</v>
+        <v>128447261</v>
       </c>
       <c r="B17" t="n">
-        <v>79702</v>
+        <v>92766</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586746</v>
+        <v>586663</v>
       </c>
       <c r="R17" t="n">
-        <v>7089860</v>
+        <v>7089829</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2259,32 +2259,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128447261</v>
+        <v>128437645</v>
       </c>
       <c r="B18" t="n">
-        <v>92754</v>
+        <v>79706</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586663</v>
+        <v>586746</v>
       </c>
       <c r="R18" t="n">
-        <v>7089829</v>
+        <v>7089860</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2359,7 +2359,7 @@
         <v>128439814</v>
       </c>
       <c r="B19" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128439094</v>
       </c>
       <c r="B20" t="n">
-        <v>78749</v>
+        <v>78753</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>128436765</v>
       </c>
       <c r="B21" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>128438427</v>
       </c>
       <c r="B22" t="n">
-        <v>92935</v>
+        <v>92947</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>128440316</v>
       </c>
       <c r="B23" t="n">
-        <v>92758</v>
+        <v>92770</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128438055</v>
       </c>
       <c r="B24" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>128437989</v>
       </c>
       <c r="B25" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>128438141</v>
       </c>
       <c r="B26" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>128437686</v>
       </c>
       <c r="B27" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>128443168</v>
       </c>
       <c r="B28" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>128439799</v>
       </c>
       <c r="B29" t="n">
-        <v>91613</v>
+        <v>91625</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>128439616</v>
       </c>
       <c r="B30" t="n">
-        <v>91613</v>
+        <v>91625</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>128439751</v>
       </c>
       <c r="B31" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3617,32 +3617,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128436152</v>
+        <v>128438005</v>
       </c>
       <c r="B32" t="n">
-        <v>79083</v>
+        <v>80221</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586699</v>
+        <v>586717</v>
       </c>
       <c r="R32" t="n">
-        <v>7089749</v>
+        <v>7089885</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3714,32 +3714,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128438005</v>
+        <v>128436148</v>
       </c>
       <c r="B33" t="n">
-        <v>80217</v>
+        <v>79706</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586717</v>
+        <v>586698</v>
       </c>
       <c r="R33" t="n">
-        <v>7089885</v>
+        <v>7089750</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128436148</v>
+        <v>128436152</v>
       </c>
       <c r="B34" t="n">
-        <v>79702</v>
+        <v>79087</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3822,21 +3822,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586698</v>
+        <v>586699</v>
       </c>
       <c r="R34" t="n">
-        <v>7089750</v>
+        <v>7089749</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3911,7 +3911,7 @@
         <v>128437925</v>
       </c>
       <c r="B35" t="n">
-        <v>92746</v>
+        <v>92758</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>128436482</v>
       </c>
       <c r="B36" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4102,10 +4102,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128436295</v>
+        <v>128436799</v>
       </c>
       <c r="B37" t="n">
-        <v>78749</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4113,21 +4113,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586729</v>
+        <v>586743</v>
       </c>
       <c r="R37" t="n">
-        <v>7089765</v>
+        <v>7089814</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4199,32 +4199,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128437746</v>
+        <v>128438053</v>
       </c>
       <c r="B38" t="n">
-        <v>91613</v>
+        <v>78844</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586698</v>
+        <v>586682</v>
       </c>
       <c r="R38" t="n">
-        <v>7089852</v>
+        <v>7089916</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4296,10 +4296,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128436799</v>
+        <v>128436295</v>
       </c>
       <c r="B39" t="n">
-        <v>79083</v>
+        <v>78753</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4307,21 +4307,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586743</v>
+        <v>586729</v>
       </c>
       <c r="R39" t="n">
-        <v>7089814</v>
+        <v>7089765</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4393,32 +4393,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128438053</v>
+        <v>128437746</v>
       </c>
       <c r="B40" t="n">
-        <v>78840</v>
+        <v>91625</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586682</v>
+        <v>586698</v>
       </c>
       <c r="R40" t="n">
-        <v>7089916</v>
+        <v>7089852</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4493,7 +4493,7 @@
         <v>128439054</v>
       </c>
       <c r="B41" t="n">
-        <v>91613</v>
+        <v>91625</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>128437630</v>
       </c>
       <c r="B42" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>128446039</v>
       </c>
       <c r="B43" t="n">
-        <v>78055</v>
+        <v>78059</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>128439342</v>
       </c>
       <c r="B44" t="n">
-        <v>91713</v>
+        <v>91725</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>128439704</v>
       </c>
       <c r="B45" t="n">
-        <v>92935</v>
+        <v>92947</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>128437765</v>
       </c>
       <c r="B46" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>128439117</v>
       </c>
       <c r="B47" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>128436111</v>
       </c>
       <c r="B48" t="n">
-        <v>92774</v>
+        <v>92780</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 38268-2025 artfynd.xlsx
+++ b/artfynd/A 38268-2025 artfynd.xlsx
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128439819</v>
+        <v>128438180</v>
       </c>
       <c r="B6" t="n">
-        <v>78753</v>
+        <v>80192</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586673</v>
+        <v>586656</v>
       </c>
       <c r="R6" t="n">
-        <v>7089842</v>
+        <v>7090016</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128438180</v>
+        <v>128439819</v>
       </c>
       <c r="B7" t="n">
-        <v>80192</v>
+        <v>78753</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,21 +1203,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586656</v>
+        <v>586673</v>
       </c>
       <c r="R7" t="n">
-        <v>7090016</v>
+        <v>7089842</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -4102,10 +4102,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128436799</v>
+        <v>128436295</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>78753</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4113,21 +4113,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586743</v>
+        <v>586729</v>
       </c>
       <c r="R37" t="n">
-        <v>7089814</v>
+        <v>7089765</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4199,32 +4199,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128438053</v>
+        <v>128437746</v>
       </c>
       <c r="B38" t="n">
-        <v>78844</v>
+        <v>91625</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586682</v>
+        <v>586698</v>
       </c>
       <c r="R38" t="n">
-        <v>7089916</v>
+        <v>7089852</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4296,10 +4296,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128436295</v>
+        <v>128436799</v>
       </c>
       <c r="B39" t="n">
-        <v>78753</v>
+        <v>79087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4307,21 +4307,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586729</v>
+        <v>586743</v>
       </c>
       <c r="R39" t="n">
-        <v>7089765</v>
+        <v>7089814</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4393,32 +4393,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128437746</v>
+        <v>128438053</v>
       </c>
       <c r="B40" t="n">
-        <v>91625</v>
+        <v>78844</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586698</v>
+        <v>586682</v>
       </c>
       <c r="R40" t="n">
-        <v>7089852</v>
+        <v>7089916</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>

--- a/artfynd/A 38268-2025 artfynd.xlsx
+++ b/artfynd/A 38268-2025 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128439941</v>
       </c>
       <c r="B3" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>128436169</v>
       </c>
       <c r="B4" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128438321</v>
       </c>
       <c r="B5" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128438180</v>
+        <v>128439819</v>
       </c>
       <c r="B6" t="n">
-        <v>80192</v>
+        <v>78755</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586656</v>
+        <v>586673</v>
       </c>
       <c r="R6" t="n">
-        <v>7090016</v>
+        <v>7089842</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128439819</v>
+        <v>128438180</v>
       </c>
       <c r="B7" t="n">
-        <v>78753</v>
+        <v>80194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,21 +1203,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586673</v>
+        <v>586656</v>
       </c>
       <c r="R7" t="n">
-        <v>7089842</v>
+        <v>7090016</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1289,32 +1289,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128440115</v>
+        <v>128440016</v>
       </c>
       <c r="B8" t="n">
-        <v>92754</v>
+        <v>78755</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586688</v>
+        <v>586691</v>
       </c>
       <c r="R8" t="n">
-        <v>7089811</v>
+        <v>7089809</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1386,32 +1386,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128440016</v>
+        <v>128437589</v>
       </c>
       <c r="B9" t="n">
-        <v>78753</v>
+        <v>91627</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586691</v>
+        <v>586739</v>
       </c>
       <c r="R9" t="n">
-        <v>7089809</v>
+        <v>7089865</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1483,32 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128437589</v>
+        <v>128440115</v>
       </c>
       <c r="B10" t="n">
-        <v>91625</v>
+        <v>92756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586739</v>
+        <v>586688</v>
       </c>
       <c r="R10" t="n">
-        <v>7089865</v>
+        <v>7089811</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1580,32 +1580,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128441773</v>
+        <v>128438132</v>
       </c>
       <c r="B11" t="n">
-        <v>92754</v>
+        <v>90499</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586682</v>
+        <v>586666</v>
       </c>
       <c r="R11" t="n">
-        <v>7089791</v>
+        <v>7089955</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1677,32 +1677,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128438132</v>
+        <v>128441773</v>
       </c>
       <c r="B12" t="n">
-        <v>90497</v>
+        <v>92756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586666</v>
+        <v>586682</v>
       </c>
       <c r="R12" t="n">
-        <v>7089955</v>
+        <v>7089791</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1777,7 +1777,7 @@
         <v>128439128</v>
       </c>
       <c r="B13" t="n">
-        <v>80228</v>
+        <v>80230</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128437499</v>
+        <v>128439671</v>
       </c>
       <c r="B14" t="n">
-        <v>92754</v>
+        <v>91627</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586750</v>
+        <v>586664</v>
       </c>
       <c r="R14" t="n">
-        <v>7089835</v>
+        <v>7089915</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128439671</v>
+        <v>128437871</v>
       </c>
       <c r="B15" t="n">
-        <v>91625</v>
+        <v>78755</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586664</v>
+        <v>586697</v>
       </c>
       <c r="R15" t="n">
-        <v>7089915</v>
+        <v>7089867</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2065,32 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128437871</v>
+        <v>128437499</v>
       </c>
       <c r="B16" t="n">
-        <v>78753</v>
+        <v>92756</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586697</v>
+        <v>586750</v>
       </c>
       <c r="R16" t="n">
-        <v>7089867</v>
+        <v>7089835</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2165,7 +2165,7 @@
         <v>128447261</v>
       </c>
       <c r="B17" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>128437645</v>
       </c>
       <c r="B18" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>128439814</v>
       </c>
       <c r="B19" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2453,32 +2453,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128439094</v>
+        <v>128436765</v>
       </c>
       <c r="B20" t="n">
-        <v>78753</v>
+        <v>91431</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586622</v>
+        <v>586735</v>
       </c>
       <c r="R20" t="n">
-        <v>7089926</v>
+        <v>7089818</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2550,32 +2550,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128436765</v>
+        <v>128439094</v>
       </c>
       <c r="B21" t="n">
-        <v>91429</v>
+        <v>78755</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586735</v>
+        <v>586622</v>
       </c>
       <c r="R21" t="n">
-        <v>7089818</v>
+        <v>7089926</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2650,7 +2650,7 @@
         <v>128438427</v>
       </c>
       <c r="B22" t="n">
-        <v>92947</v>
+        <v>92949</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>128440316</v>
       </c>
       <c r="B23" t="n">
-        <v>92770</v>
+        <v>92772</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128438055</v>
       </c>
       <c r="B24" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>128437989</v>
       </c>
       <c r="B25" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>128438141</v>
       </c>
       <c r="B26" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>128437686</v>
       </c>
       <c r="B27" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>128443168</v>
       </c>
       <c r="B28" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>128439799</v>
       </c>
       <c r="B29" t="n">
-        <v>91625</v>
+        <v>91627</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>128439616</v>
       </c>
       <c r="B30" t="n">
-        <v>91625</v>
+        <v>91627</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>128439751</v>
       </c>
       <c r="B31" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3617,32 +3617,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128438005</v>
+        <v>128436152</v>
       </c>
       <c r="B32" t="n">
-        <v>80221</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586717</v>
+        <v>586699</v>
       </c>
       <c r="R32" t="n">
-        <v>7089885</v>
+        <v>7089749</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3714,32 +3714,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128436148</v>
+        <v>128438005</v>
       </c>
       <c r="B33" t="n">
-        <v>79706</v>
+        <v>80223</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586698</v>
+        <v>586717</v>
       </c>
       <c r="R33" t="n">
-        <v>7089750</v>
+        <v>7089885</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128436152</v>
+        <v>128436148</v>
       </c>
       <c r="B34" t="n">
-        <v>79087</v>
+        <v>79708</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3822,21 +3822,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586699</v>
+        <v>586698</v>
       </c>
       <c r="R34" t="n">
-        <v>7089749</v>
+        <v>7089750</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3911,7 +3911,7 @@
         <v>128437925</v>
       </c>
       <c r="B35" t="n">
-        <v>92758</v>
+        <v>92760</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>128436482</v>
       </c>
       <c r="B36" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>128436295</v>
       </c>
       <c r="B37" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>128437746</v>
       </c>
       <c r="B38" t="n">
-        <v>91625</v>
+        <v>91627</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>128436799</v>
       </c>
       <c r="B39" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>128438053</v>
       </c>
       <c r="B40" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>128439054</v>
       </c>
       <c r="B41" t="n">
-        <v>91625</v>
+        <v>91627</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>128437630</v>
       </c>
       <c r="B42" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>128446039</v>
       </c>
       <c r="B43" t="n">
-        <v>78059</v>
+        <v>78061</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>128439342</v>
       </c>
       <c r="B44" t="n">
-        <v>91725</v>
+        <v>91727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>128439704</v>
       </c>
       <c r="B45" t="n">
-        <v>92947</v>
+        <v>92949</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>128437765</v>
       </c>
       <c r="B46" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>128439117</v>
       </c>
       <c r="B47" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>128436111</v>
       </c>
       <c r="B48" t="n">
-        <v>92780</v>
+        <v>92782</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 38268-2025 artfynd.xlsx
+++ b/artfynd/A 38268-2025 artfynd.xlsx
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128439819</v>
+        <v>128438180</v>
       </c>
       <c r="B6" t="n">
-        <v>78755</v>
+        <v>80194</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586673</v>
+        <v>586656</v>
       </c>
       <c r="R6" t="n">
-        <v>7089842</v>
+        <v>7090016</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128438180</v>
+        <v>128439819</v>
       </c>
       <c r="B7" t="n">
-        <v>80194</v>
+        <v>78755</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,21 +1203,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586656</v>
+        <v>586673</v>
       </c>
       <c r="R7" t="n">
-        <v>7090016</v>
+        <v>7089842</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128439671</v>
+        <v>128437499</v>
       </c>
       <c r="B14" t="n">
-        <v>91627</v>
+        <v>92756</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586664</v>
+        <v>586750</v>
       </c>
       <c r="R14" t="n">
-        <v>7089915</v>
+        <v>7089835</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128437871</v>
+        <v>128439671</v>
       </c>
       <c r="B15" t="n">
-        <v>78755</v>
+        <v>91627</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586697</v>
+        <v>586664</v>
       </c>
       <c r="R15" t="n">
-        <v>7089867</v>
+        <v>7089915</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2065,32 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128437499</v>
+        <v>128437871</v>
       </c>
       <c r="B16" t="n">
-        <v>92756</v>
+        <v>78755</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586750</v>
+        <v>586697</v>
       </c>
       <c r="R16" t="n">
-        <v>7089835</v>
+        <v>7089867</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2453,32 +2453,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128436765</v>
+        <v>128439094</v>
       </c>
       <c r="B20" t="n">
-        <v>91431</v>
+        <v>78755</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586735</v>
+        <v>586622</v>
       </c>
       <c r="R20" t="n">
-        <v>7089818</v>
+        <v>7089926</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2550,32 +2550,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128439094</v>
+        <v>128436765</v>
       </c>
       <c r="B21" t="n">
-        <v>78755</v>
+        <v>91431</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586622</v>
+        <v>586735</v>
       </c>
       <c r="R21" t="n">
-        <v>7089926</v>
+        <v>7089818</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2841,32 +2841,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128438055</v>
+        <v>128437989</v>
       </c>
       <c r="B24" t="n">
-        <v>92756</v>
+        <v>80194</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586682</v>
+        <v>586701</v>
       </c>
       <c r="R24" t="n">
-        <v>7089917</v>
+        <v>7089891</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2938,32 +2938,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128437989</v>
+        <v>128438055</v>
       </c>
       <c r="B25" t="n">
-        <v>80194</v>
+        <v>92756</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586701</v>
+        <v>586682</v>
       </c>
       <c r="R25" t="n">
-        <v>7089891</v>
+        <v>7089917</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3035,32 +3035,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128438141</v>
+        <v>128443168</v>
       </c>
       <c r="B26" t="n">
-        <v>80194</v>
+        <v>92756</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,7 +3073,7 @@
         <v>586666</v>
       </c>
       <c r="R26" t="n">
-        <v>7089955</v>
+        <v>7089771</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128437686</v>
+        <v>128438141</v>
       </c>
       <c r="B27" t="n">
-        <v>79708</v>
+        <v>80194</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3143,21 +3143,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3167,10 +3167,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586741</v>
+        <v>586666</v>
       </c>
       <c r="R27" t="n">
-        <v>7089870</v>
+        <v>7089955</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3229,32 +3229,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128443168</v>
+        <v>128437686</v>
       </c>
       <c r="B28" t="n">
-        <v>92756</v>
+        <v>79708</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586666</v>
+        <v>586741</v>
       </c>
       <c r="R28" t="n">
-        <v>7089771</v>
+        <v>7089870</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3520,10 +3520,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128439751</v>
+        <v>128436152</v>
       </c>
       <c r="B31" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3531,21 +3531,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3555,10 +3555,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586681</v>
+        <v>586699</v>
       </c>
       <c r="R31" t="n">
-        <v>7089872</v>
+        <v>7089749</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3617,10 +3617,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128436152</v>
+        <v>128439751</v>
       </c>
       <c r="B32" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3628,21 +3628,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586699</v>
+        <v>586681</v>
       </c>
       <c r="R32" t="n">
-        <v>7089749</v>
+        <v>7089872</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4102,10 +4102,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128436295</v>
+        <v>128436799</v>
       </c>
       <c r="B37" t="n">
-        <v>78755</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4113,21 +4113,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586729</v>
+        <v>586743</v>
       </c>
       <c r="R37" t="n">
-        <v>7089765</v>
+        <v>7089814</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4199,32 +4199,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128437746</v>
+        <v>128438053</v>
       </c>
       <c r="B38" t="n">
-        <v>91627</v>
+        <v>78846</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586698</v>
+        <v>586682</v>
       </c>
       <c r="R38" t="n">
-        <v>7089852</v>
+        <v>7089916</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4296,10 +4296,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128436799</v>
+        <v>128436295</v>
       </c>
       <c r="B39" t="n">
-        <v>79089</v>
+        <v>78755</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4307,21 +4307,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586743</v>
+        <v>586729</v>
       </c>
       <c r="R39" t="n">
-        <v>7089814</v>
+        <v>7089765</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4393,32 +4393,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128438053</v>
+        <v>128437746</v>
       </c>
       <c r="B40" t="n">
-        <v>78846</v>
+        <v>91627</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586682</v>
+        <v>586698</v>
       </c>
       <c r="R40" t="n">
-        <v>7089916</v>
+        <v>7089852</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4490,32 +4490,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128439054</v>
+        <v>128437630</v>
       </c>
       <c r="B41" t="n">
-        <v>91627</v>
+        <v>78846</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586635</v>
+        <v>586750</v>
       </c>
       <c r="R41" t="n">
-        <v>7089949</v>
+        <v>7089861</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4587,10 +4587,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128437630</v>
+        <v>128446039</v>
       </c>
       <c r="B42" t="n">
-        <v>78846</v>
+        <v>78061</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4598,21 +4598,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586750</v>
+        <v>586654</v>
       </c>
       <c r="R42" t="n">
-        <v>7089861</v>
+        <v>7089830</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4684,32 +4684,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128446039</v>
+        <v>128439054</v>
       </c>
       <c r="B43" t="n">
-        <v>78061</v>
+        <v>91627</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6487</v>
+        <v>1503</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586654</v>
+        <v>586635</v>
       </c>
       <c r="R43" t="n">
-        <v>7089830</v>
+        <v>7089949</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>

--- a/artfynd/A 38268-2025 artfynd.xlsx
+++ b/artfynd/A 38268-2025 artfynd.xlsx
@@ -3326,32 +3326,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128439799</v>
+        <v>128436152</v>
       </c>
       <c r="B29" t="n">
-        <v>91627</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586664</v>
+        <v>586699</v>
       </c>
       <c r="R29" t="n">
-        <v>7089845</v>
+        <v>7089749</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3423,7 +3423,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128439616</v>
+        <v>128439799</v>
       </c>
       <c r="B30" t="n">
         <v>91627</v>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>586660</v>
+        <v>586664</v>
       </c>
       <c r="R30" t="n">
-        <v>7089907</v>
+        <v>7089845</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3520,32 +3520,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128436152</v>
+        <v>128439616</v>
       </c>
       <c r="B31" t="n">
-        <v>79089</v>
+        <v>91627</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3555,10 +3555,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586699</v>
+        <v>586660</v>
       </c>
       <c r="R31" t="n">
-        <v>7089749</v>
+        <v>7089907</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4490,32 +4490,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128437630</v>
+        <v>128439054</v>
       </c>
       <c r="B41" t="n">
-        <v>78846</v>
+        <v>91627</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586750</v>
+        <v>586635</v>
       </c>
       <c r="R41" t="n">
-        <v>7089861</v>
+        <v>7089949</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4587,10 +4587,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128446039</v>
+        <v>128437630</v>
       </c>
       <c r="B42" t="n">
-        <v>78061</v>
+        <v>78846</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4598,21 +4598,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586654</v>
+        <v>586750</v>
       </c>
       <c r="R42" t="n">
-        <v>7089830</v>
+        <v>7089861</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4684,32 +4684,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128439054</v>
+        <v>128446039</v>
       </c>
       <c r="B43" t="n">
-        <v>91627</v>
+        <v>78061</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1503</v>
+        <v>6487</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586635</v>
+        <v>586654</v>
       </c>
       <c r="R43" t="n">
-        <v>7089949</v>
+        <v>7089830</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>

--- a/artfynd/A 38268-2025 artfynd.xlsx
+++ b/artfynd/A 38268-2025 artfynd.xlsx
@@ -901,32 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128436169</v>
+        <v>128438321</v>
       </c>
       <c r="B4" t="n">
-        <v>92756</v>
+        <v>78755</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586711</v>
+        <v>586605</v>
       </c>
       <c r="R4" t="n">
-        <v>7089755</v>
+        <v>7090026</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -998,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128438321</v>
+        <v>128436169</v>
       </c>
       <c r="B5" t="n">
-        <v>78755</v>
+        <v>92757</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586605</v>
+        <v>586711</v>
       </c>
       <c r="R5" t="n">
-        <v>7090026</v>
+        <v>7089755</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1289,32 +1289,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128440016</v>
+        <v>128440115</v>
       </c>
       <c r="B8" t="n">
-        <v>78755</v>
+        <v>92757</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586691</v>
+        <v>586688</v>
       </c>
       <c r="R8" t="n">
-        <v>7089809</v>
+        <v>7089811</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1386,32 +1386,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128437589</v>
+        <v>128440016</v>
       </c>
       <c r="B9" t="n">
-        <v>91627</v>
+        <v>78755</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586739</v>
+        <v>586691</v>
       </c>
       <c r="R9" t="n">
-        <v>7089865</v>
+        <v>7089809</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1483,32 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128440115</v>
+        <v>128437589</v>
       </c>
       <c r="B10" t="n">
-        <v>92756</v>
+        <v>91628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586688</v>
+        <v>586739</v>
       </c>
       <c r="R10" t="n">
-        <v>7089811</v>
+        <v>7089865</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1677,10 +1677,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128441773</v>
+        <v>128439128</v>
       </c>
       <c r="B12" t="n">
-        <v>92756</v>
+        <v>80230</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1688,21 +1688,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586682</v>
+        <v>586657</v>
       </c>
       <c r="R12" t="n">
-        <v>7089791</v>
+        <v>7089905</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1774,10 +1774,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128439128</v>
+        <v>128441773</v>
       </c>
       <c r="B13" t="n">
-        <v>80230</v>
+        <v>92757</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1785,21 +1785,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586657</v>
+        <v>586682</v>
       </c>
       <c r="R13" t="n">
-        <v>7089905</v>
+        <v>7089791</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128437499</v>
+        <v>128439671</v>
       </c>
       <c r="B14" t="n">
-        <v>92756</v>
+        <v>91628</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586750</v>
+        <v>586664</v>
       </c>
       <c r="R14" t="n">
-        <v>7089835</v>
+        <v>7089915</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128439671</v>
+        <v>128437499</v>
       </c>
       <c r="B15" t="n">
-        <v>91627</v>
+        <v>92757</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586664</v>
+        <v>586750</v>
       </c>
       <c r="R15" t="n">
-        <v>7089915</v>
+        <v>7089835</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2162,32 +2162,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128447261</v>
+        <v>128437645</v>
       </c>
       <c r="B17" t="n">
-        <v>92768</v>
+        <v>79708</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586663</v>
+        <v>586746</v>
       </c>
       <c r="R17" t="n">
-        <v>7089829</v>
+        <v>7089860</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2259,32 +2259,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128437645</v>
+        <v>128447261</v>
       </c>
       <c r="B18" t="n">
-        <v>79708</v>
+        <v>92769</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586746</v>
+        <v>586663</v>
       </c>
       <c r="R18" t="n">
-        <v>7089860</v>
+        <v>7089829</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2553,7 +2553,7 @@
         <v>128436765</v>
       </c>
       <c r="B21" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>128438427</v>
       </c>
       <c r="B22" t="n">
-        <v>92949</v>
+        <v>92950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>128440316</v>
       </c>
       <c r="B23" t="n">
-        <v>92772</v>
+        <v>92773</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2841,32 +2841,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128437989</v>
+        <v>128438055</v>
       </c>
       <c r="B24" t="n">
-        <v>80194</v>
+        <v>92757</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586701</v>
+        <v>586682</v>
       </c>
       <c r="R24" t="n">
-        <v>7089891</v>
+        <v>7089917</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2938,32 +2938,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128438055</v>
+        <v>128437989</v>
       </c>
       <c r="B25" t="n">
-        <v>92756</v>
+        <v>80194</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586682</v>
+        <v>586701</v>
       </c>
       <c r="R25" t="n">
-        <v>7089917</v>
+        <v>7089891</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3035,32 +3035,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128443168</v>
+        <v>128438141</v>
       </c>
       <c r="B26" t="n">
-        <v>92756</v>
+        <v>80194</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,7 +3073,7 @@
         <v>586666</v>
       </c>
       <c r="R26" t="n">
-        <v>7089771</v>
+        <v>7089955</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128438141</v>
+        <v>128437686</v>
       </c>
       <c r="B27" t="n">
-        <v>80194</v>
+        <v>79708</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3143,21 +3143,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3167,10 +3167,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586666</v>
+        <v>586741</v>
       </c>
       <c r="R27" t="n">
-        <v>7089955</v>
+        <v>7089870</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3229,32 +3229,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128437686</v>
+        <v>128443168</v>
       </c>
       <c r="B28" t="n">
-        <v>79708</v>
+        <v>92757</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586741</v>
+        <v>586666</v>
       </c>
       <c r="R28" t="n">
-        <v>7089870</v>
+        <v>7089771</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3326,32 +3326,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128436152</v>
+        <v>128439799</v>
       </c>
       <c r="B29" t="n">
-        <v>79089</v>
+        <v>91628</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586699</v>
+        <v>586664</v>
       </c>
       <c r="R29" t="n">
-        <v>7089749</v>
+        <v>7089845</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3423,10 +3423,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128439799</v>
+        <v>128439616</v>
       </c>
       <c r="B30" t="n">
-        <v>91627</v>
+        <v>91628</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>586664</v>
+        <v>586660</v>
       </c>
       <c r="R30" t="n">
-        <v>7089845</v>
+        <v>7089907</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3520,32 +3520,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128439616</v>
+        <v>128436152</v>
       </c>
       <c r="B31" t="n">
-        <v>91627</v>
+        <v>79089</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3555,10 +3555,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586660</v>
+        <v>586699</v>
       </c>
       <c r="R31" t="n">
-        <v>7089907</v>
+        <v>7089749</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3617,32 +3617,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128439751</v>
+        <v>128438005</v>
       </c>
       <c r="B32" t="n">
-        <v>79708</v>
+        <v>80223</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586681</v>
+        <v>586717</v>
       </c>
       <c r="R32" t="n">
-        <v>7089872</v>
+        <v>7089885</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3714,32 +3714,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128438005</v>
+        <v>128439751</v>
       </c>
       <c r="B33" t="n">
-        <v>80223</v>
+        <v>79708</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586717</v>
+        <v>586681</v>
       </c>
       <c r="R33" t="n">
-        <v>7089885</v>
+        <v>7089872</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3911,7 +3911,7 @@
         <v>128437925</v>
       </c>
       <c r="B35" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4102,32 +4102,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128436799</v>
+        <v>128437746</v>
       </c>
       <c r="B37" t="n">
-        <v>79089</v>
+        <v>91628</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586743</v>
+        <v>586698</v>
       </c>
       <c r="R37" t="n">
-        <v>7089814</v>
+        <v>7089852</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4199,10 +4199,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128438053</v>
+        <v>128436799</v>
       </c>
       <c r="B38" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4210,21 +4210,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586682</v>
+        <v>586743</v>
       </c>
       <c r="R38" t="n">
-        <v>7089916</v>
+        <v>7089814</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4296,10 +4296,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128436295</v>
+        <v>128438053</v>
       </c>
       <c r="B39" t="n">
-        <v>78755</v>
+        <v>78846</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4307,21 +4307,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586729</v>
+        <v>586682</v>
       </c>
       <c r="R39" t="n">
-        <v>7089765</v>
+        <v>7089916</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4393,32 +4393,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128437746</v>
+        <v>128436295</v>
       </c>
       <c r="B40" t="n">
-        <v>91627</v>
+        <v>78755</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586698</v>
+        <v>586729</v>
       </c>
       <c r="R40" t="n">
-        <v>7089852</v>
+        <v>7089765</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4493,7 +4493,7 @@
         <v>128439054</v>
       </c>
       <c r="B41" t="n">
-        <v>91627</v>
+        <v>91628</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4781,32 +4781,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128439342</v>
+        <v>128439704</v>
       </c>
       <c r="B44" t="n">
-        <v>91727</v>
+        <v>92950</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4816,10 +4816,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586657</v>
+        <v>586666</v>
       </c>
       <c r="R44" t="n">
-        <v>7089895</v>
+        <v>7089914</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4878,10 +4878,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128439704</v>
+        <v>128437765</v>
       </c>
       <c r="B45" t="n">
-        <v>92949</v>
+        <v>79089</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4889,21 +4889,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586666</v>
+        <v>586703</v>
       </c>
       <c r="R45" t="n">
-        <v>7089914</v>
+        <v>7089847</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -4975,10 +4975,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128437765</v>
+        <v>128439117</v>
       </c>
       <c r="B46" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4986,21 +4986,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586703</v>
+        <v>586650</v>
       </c>
       <c r="R46" t="n">
-        <v>7089847</v>
+        <v>7089902</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5072,32 +5072,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128439117</v>
+        <v>128439342</v>
       </c>
       <c r="B47" t="n">
-        <v>80194</v>
+        <v>91728</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>65</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586650</v>
+        <v>586657</v>
       </c>
       <c r="R47" t="n">
-        <v>7089902</v>
+        <v>7089895</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5172,7 +5172,7 @@
         <v>128436111</v>
       </c>
       <c r="B48" t="n">
-        <v>92782</v>
+        <v>92783</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 38268-2025 artfynd.xlsx
+++ b/artfynd/A 38268-2025 artfynd.xlsx
@@ -1289,32 +1289,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128440115</v>
+        <v>128437589</v>
       </c>
       <c r="B8" t="n">
-        <v>92757</v>
+        <v>91628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586688</v>
+        <v>586739</v>
       </c>
       <c r="R8" t="n">
-        <v>7089811</v>
+        <v>7089865</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1483,32 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128437589</v>
+        <v>128440115</v>
       </c>
       <c r="B10" t="n">
-        <v>91628</v>
+        <v>92757</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586739</v>
+        <v>586688</v>
       </c>
       <c r="R10" t="n">
-        <v>7089865</v>
+        <v>7089811</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -2841,32 +2841,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128438055</v>
+        <v>128437989</v>
       </c>
       <c r="B24" t="n">
-        <v>92757</v>
+        <v>80194</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586682</v>
+        <v>586701</v>
       </c>
       <c r="R24" t="n">
-        <v>7089917</v>
+        <v>7089891</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2938,32 +2938,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128437989</v>
+        <v>128438055</v>
       </c>
       <c r="B25" t="n">
-        <v>80194</v>
+        <v>92757</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586701</v>
+        <v>586682</v>
       </c>
       <c r="R25" t="n">
-        <v>7089891</v>
+        <v>7089917</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -4102,32 +4102,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128437746</v>
+        <v>128438053</v>
       </c>
       <c r="B37" t="n">
-        <v>91628</v>
+        <v>78846</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586698</v>
+        <v>586682</v>
       </c>
       <c r="R37" t="n">
-        <v>7089852</v>
+        <v>7089916</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4199,10 +4199,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128436799</v>
+        <v>128436295</v>
       </c>
       <c r="B38" t="n">
-        <v>79089</v>
+        <v>78755</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4210,21 +4210,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586743</v>
+        <v>586729</v>
       </c>
       <c r="R38" t="n">
-        <v>7089814</v>
+        <v>7089765</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4296,32 +4296,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128438053</v>
+        <v>128437746</v>
       </c>
       <c r="B39" t="n">
-        <v>78846</v>
+        <v>91628</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586682</v>
+        <v>586698</v>
       </c>
       <c r="R39" t="n">
-        <v>7089916</v>
+        <v>7089852</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128436295</v>
+        <v>128436799</v>
       </c>
       <c r="B40" t="n">
-        <v>78755</v>
+        <v>79089</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4404,21 +4404,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586729</v>
+        <v>586743</v>
       </c>
       <c r="R40" t="n">
-        <v>7089765</v>
+        <v>7089814</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5172,7 +5172,7 @@
         <v>128436111</v>
       </c>
       <c r="B48" t="n">
-        <v>92783</v>
+        <v>92810</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 38268-2025 artfynd.xlsx
+++ b/artfynd/A 38268-2025 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128439941</v>
       </c>
       <c r="B3" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>128438321</v>
       </c>
       <c r="B4" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128436169</v>
       </c>
       <c r="B5" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128438180</v>
+        <v>128439819</v>
       </c>
       <c r="B6" t="n">
-        <v>80194</v>
+        <v>78782</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586656</v>
+        <v>586673</v>
       </c>
       <c r="R6" t="n">
-        <v>7090016</v>
+        <v>7089842</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128439819</v>
+        <v>128438180</v>
       </c>
       <c r="B7" t="n">
-        <v>78755</v>
+        <v>80221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,21 +1203,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586673</v>
+        <v>586656</v>
       </c>
       <c r="R7" t="n">
-        <v>7089842</v>
+        <v>7090016</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1289,32 +1289,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128437589</v>
+        <v>128440016</v>
       </c>
       <c r="B8" t="n">
-        <v>91628</v>
+        <v>78782</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586739</v>
+        <v>586691</v>
       </c>
       <c r="R8" t="n">
-        <v>7089865</v>
+        <v>7089809</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1386,32 +1386,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128440016</v>
+        <v>128437589</v>
       </c>
       <c r="B9" t="n">
-        <v>78755</v>
+        <v>91655</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586691</v>
+        <v>586739</v>
       </c>
       <c r="R9" t="n">
-        <v>7089809</v>
+        <v>7089865</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1486,7 +1486,7 @@
         <v>128440115</v>
       </c>
       <c r="B10" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>128438132</v>
       </c>
       <c r="B11" t="n">
-        <v>90499</v>
+        <v>90526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>128439128</v>
       </c>
       <c r="B12" t="n">
-        <v>80230</v>
+        <v>80257</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>128441773</v>
       </c>
       <c r="B13" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>128439671</v>
       </c>
       <c r="B14" t="n">
-        <v>91628</v>
+        <v>91655</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128437499</v>
+        <v>128437871</v>
       </c>
       <c r="B15" t="n">
-        <v>92757</v>
+        <v>78782</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586750</v>
+        <v>586697</v>
       </c>
       <c r="R15" t="n">
-        <v>7089835</v>
+        <v>7089867</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2065,32 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128437871</v>
+        <v>128437499</v>
       </c>
       <c r="B16" t="n">
-        <v>78755</v>
+        <v>92784</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586697</v>
+        <v>586750</v>
       </c>
       <c r="R16" t="n">
-        <v>7089867</v>
+        <v>7089835</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2162,32 +2162,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128437645</v>
+        <v>128447261</v>
       </c>
       <c r="B17" t="n">
-        <v>79708</v>
+        <v>92796</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586746</v>
+        <v>586663</v>
       </c>
       <c r="R17" t="n">
-        <v>7089860</v>
+        <v>7089829</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2259,32 +2259,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128447261</v>
+        <v>128437645</v>
       </c>
       <c r="B18" t="n">
-        <v>92769</v>
+        <v>79735</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586663</v>
+        <v>586746</v>
       </c>
       <c r="R18" t="n">
-        <v>7089829</v>
+        <v>7089860</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2359,7 +2359,7 @@
         <v>128439814</v>
       </c>
       <c r="B19" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128439094</v>
       </c>
       <c r="B20" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>128436765</v>
       </c>
       <c r="B21" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>128438427</v>
       </c>
       <c r="B22" t="n">
-        <v>92950</v>
+        <v>92977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>128440316</v>
       </c>
       <c r="B23" t="n">
-        <v>92773</v>
+        <v>92800</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2841,32 +2841,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128437989</v>
+        <v>128438055</v>
       </c>
       <c r="B24" t="n">
-        <v>80194</v>
+        <v>92784</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586701</v>
+        <v>586682</v>
       </c>
       <c r="R24" t="n">
-        <v>7089891</v>
+        <v>7089917</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2938,32 +2938,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128438055</v>
+        <v>128437989</v>
       </c>
       <c r="B25" t="n">
-        <v>92757</v>
+        <v>80221</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586682</v>
+        <v>586701</v>
       </c>
       <c r="R25" t="n">
-        <v>7089917</v>
+        <v>7089891</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3038,7 +3038,7 @@
         <v>128438141</v>
       </c>
       <c r="B26" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>128437686</v>
       </c>
       <c r="B27" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>128443168</v>
       </c>
       <c r="B28" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>128439799</v>
       </c>
       <c r="B29" t="n">
-        <v>91628</v>
+        <v>91655</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>128439616</v>
       </c>
       <c r="B30" t="n">
-        <v>91628</v>
+        <v>91655</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3520,32 +3520,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128436152</v>
+        <v>128438005</v>
       </c>
       <c r="B31" t="n">
-        <v>79089</v>
+        <v>80250</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3555,10 +3555,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586699</v>
+        <v>586717</v>
       </c>
       <c r="R31" t="n">
-        <v>7089749</v>
+        <v>7089885</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3617,32 +3617,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128438005</v>
+        <v>128439751</v>
       </c>
       <c r="B32" t="n">
-        <v>80223</v>
+        <v>79735</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586717</v>
+        <v>586681</v>
       </c>
       <c r="R32" t="n">
-        <v>7089885</v>
+        <v>7089872</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3714,10 +3714,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128439751</v>
+        <v>128436152</v>
       </c>
       <c r="B33" t="n">
-        <v>79708</v>
+        <v>79116</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3725,21 +3725,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586681</v>
+        <v>586699</v>
       </c>
       <c r="R33" t="n">
-        <v>7089872</v>
+        <v>7089749</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3814,7 +3814,7 @@
         <v>128436148</v>
       </c>
       <c r="B34" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>128437925</v>
       </c>
       <c r="B35" t="n">
-        <v>92761</v>
+        <v>92788</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>128436482</v>
       </c>
       <c r="B36" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4102,10 +4102,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128438053</v>
+        <v>128436295</v>
       </c>
       <c r="B37" t="n">
-        <v>78846</v>
+        <v>78782</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4113,21 +4113,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586682</v>
+        <v>586729</v>
       </c>
       <c r="R37" t="n">
-        <v>7089916</v>
+        <v>7089765</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4199,32 +4199,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128436295</v>
+        <v>128437746</v>
       </c>
       <c r="B38" t="n">
-        <v>78755</v>
+        <v>91655</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586729</v>
+        <v>586698</v>
       </c>
       <c r="R38" t="n">
-        <v>7089765</v>
+        <v>7089852</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4296,32 +4296,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128437746</v>
+        <v>128436799</v>
       </c>
       <c r="B39" t="n">
-        <v>91628</v>
+        <v>79116</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586698</v>
+        <v>586743</v>
       </c>
       <c r="R39" t="n">
-        <v>7089852</v>
+        <v>7089814</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128436799</v>
+        <v>128438053</v>
       </c>
       <c r="B40" t="n">
-        <v>79089</v>
+        <v>78873</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4404,21 +4404,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586743</v>
+        <v>586682</v>
       </c>
       <c r="R40" t="n">
-        <v>7089814</v>
+        <v>7089916</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4493,7 +4493,7 @@
         <v>128439054</v>
       </c>
       <c r="B41" t="n">
-        <v>91628</v>
+        <v>91655</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4587,10 +4587,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128437630</v>
+        <v>128446039</v>
       </c>
       <c r="B42" t="n">
-        <v>78846</v>
+        <v>78088</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4598,21 +4598,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586750</v>
+        <v>586654</v>
       </c>
       <c r="R42" t="n">
-        <v>7089861</v>
+        <v>7089830</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4684,10 +4684,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128446039</v>
+        <v>128437630</v>
       </c>
       <c r="B43" t="n">
-        <v>78061</v>
+        <v>78873</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4695,21 +4695,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586654</v>
+        <v>586750</v>
       </c>
       <c r="R43" t="n">
-        <v>7089830</v>
+        <v>7089861</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4781,10 +4781,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128439704</v>
+        <v>128437765</v>
       </c>
       <c r="B44" t="n">
-        <v>92950</v>
+        <v>79116</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4792,21 +4792,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4816,10 +4816,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586666</v>
+        <v>586703</v>
       </c>
       <c r="R44" t="n">
-        <v>7089914</v>
+        <v>7089847</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4878,10 +4878,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128437765</v>
+        <v>128439117</v>
       </c>
       <c r="B45" t="n">
-        <v>79089</v>
+        <v>80221</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4889,21 +4889,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586703</v>
+        <v>586650</v>
       </c>
       <c r="R45" t="n">
-        <v>7089847</v>
+        <v>7089902</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -4975,10 +4975,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128439117</v>
+        <v>128439704</v>
       </c>
       <c r="B46" t="n">
-        <v>80194</v>
+        <v>92977</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4986,21 +4986,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586650</v>
+        <v>586666</v>
       </c>
       <c r="R46" t="n">
-        <v>7089902</v>
+        <v>7089914</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5075,7 +5075,7 @@
         <v>128439342</v>
       </c>
       <c r="B47" t="n">
-        <v>91728</v>
+        <v>91755</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 38268-2025 artfynd.xlsx
+++ b/artfynd/A 38268-2025 artfynd.xlsx
@@ -901,32 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128438321</v>
+        <v>128436169</v>
       </c>
       <c r="B4" t="n">
-        <v>78782</v>
+        <v>92784</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586605</v>
+        <v>586711</v>
       </c>
       <c r="R4" t="n">
-        <v>7090026</v>
+        <v>7089755</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -998,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128436169</v>
+        <v>128438321</v>
       </c>
       <c r="B5" t="n">
-        <v>92784</v>
+        <v>78782</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586711</v>
+        <v>586605</v>
       </c>
       <c r="R5" t="n">
-        <v>7089755</v>
+        <v>7090026</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1289,32 +1289,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128440016</v>
+        <v>128440115</v>
       </c>
       <c r="B8" t="n">
-        <v>78782</v>
+        <v>92784</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586691</v>
+        <v>586688</v>
       </c>
       <c r="R8" t="n">
-        <v>7089809</v>
+        <v>7089811</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1386,32 +1386,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128437589</v>
+        <v>128440016</v>
       </c>
       <c r="B9" t="n">
-        <v>91655</v>
+        <v>78782</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586739</v>
+        <v>586691</v>
       </c>
       <c r="R9" t="n">
-        <v>7089865</v>
+        <v>7089809</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1483,32 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128440115</v>
+        <v>128437589</v>
       </c>
       <c r="B10" t="n">
-        <v>92784</v>
+        <v>91655</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586688</v>
+        <v>586739</v>
       </c>
       <c r="R10" t="n">
-        <v>7089811</v>
+        <v>7089865</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1580,32 +1580,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128438132</v>
+        <v>128441773</v>
       </c>
       <c r="B11" t="n">
-        <v>90526</v>
+        <v>92784</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586666</v>
+        <v>586682</v>
       </c>
       <c r="R11" t="n">
-        <v>7089955</v>
+        <v>7089791</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1774,32 +1774,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128441773</v>
+        <v>128438132</v>
       </c>
       <c r="B13" t="n">
-        <v>92784</v>
+        <v>90526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586682</v>
+        <v>586666</v>
       </c>
       <c r="R13" t="n">
-        <v>7089791</v>
+        <v>7089955</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128439671</v>
+        <v>128437499</v>
       </c>
       <c r="B14" t="n">
-        <v>91655</v>
+        <v>92784</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586664</v>
+        <v>586750</v>
       </c>
       <c r="R14" t="n">
-        <v>7089915</v>
+        <v>7089835</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128437871</v>
+        <v>128439671</v>
       </c>
       <c r="B15" t="n">
-        <v>78782</v>
+        <v>91655</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586697</v>
+        <v>586664</v>
       </c>
       <c r="R15" t="n">
-        <v>7089867</v>
+        <v>7089915</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2065,32 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128437499</v>
+        <v>128437871</v>
       </c>
       <c r="B16" t="n">
-        <v>92784</v>
+        <v>78782</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586750</v>
+        <v>586697</v>
       </c>
       <c r="R16" t="n">
-        <v>7089835</v>
+        <v>7089867</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2162,32 +2162,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128447261</v>
+        <v>128437645</v>
       </c>
       <c r="B17" t="n">
-        <v>92796</v>
+        <v>79735</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586663</v>
+        <v>586746</v>
       </c>
       <c r="R17" t="n">
-        <v>7089829</v>
+        <v>7089860</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2259,32 +2259,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128437645</v>
+        <v>128447261</v>
       </c>
       <c r="B18" t="n">
-        <v>79735</v>
+        <v>92796</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586746</v>
+        <v>586663</v>
       </c>
       <c r="R18" t="n">
-        <v>7089860</v>
+        <v>7089829</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -3035,32 +3035,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128438141</v>
+        <v>128443168</v>
       </c>
       <c r="B26" t="n">
-        <v>80221</v>
+        <v>92784</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,7 +3073,7 @@
         <v>586666</v>
       </c>
       <c r="R26" t="n">
-        <v>7089955</v>
+        <v>7089771</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128437686</v>
+        <v>128438141</v>
       </c>
       <c r="B27" t="n">
-        <v>79735</v>
+        <v>80221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3143,21 +3143,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3167,10 +3167,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586741</v>
+        <v>586666</v>
       </c>
       <c r="R27" t="n">
-        <v>7089870</v>
+        <v>7089955</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3229,32 +3229,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128443168</v>
+        <v>128437686</v>
       </c>
       <c r="B28" t="n">
-        <v>92784</v>
+        <v>79735</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586666</v>
+        <v>586741</v>
       </c>
       <c r="R28" t="n">
-        <v>7089771</v>
+        <v>7089870</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3326,32 +3326,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128439799</v>
+        <v>128439751</v>
       </c>
       <c r="B29" t="n">
-        <v>91655</v>
+        <v>79735</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586664</v>
+        <v>586681</v>
       </c>
       <c r="R29" t="n">
-        <v>7089845</v>
+        <v>7089872</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3423,32 +3423,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128439616</v>
+        <v>128438005</v>
       </c>
       <c r="B30" t="n">
-        <v>91655</v>
+        <v>80250</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1503</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>586660</v>
+        <v>586717</v>
       </c>
       <c r="R30" t="n">
-        <v>7089907</v>
+        <v>7089885</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3520,32 +3520,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128438005</v>
+        <v>128436148</v>
       </c>
       <c r="B31" t="n">
-        <v>80250</v>
+        <v>79735</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3555,10 +3555,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586717</v>
+        <v>586698</v>
       </c>
       <c r="R31" t="n">
-        <v>7089885</v>
+        <v>7089750</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3617,10 +3617,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128439751</v>
+        <v>128436152</v>
       </c>
       <c r="B32" t="n">
-        <v>79735</v>
+        <v>79116</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3628,21 +3628,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586681</v>
+        <v>586699</v>
       </c>
       <c r="R32" t="n">
-        <v>7089872</v>
+        <v>7089749</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3714,32 +3714,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128436152</v>
+        <v>128439799</v>
       </c>
       <c r="B33" t="n">
-        <v>79116</v>
+        <v>91655</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586699</v>
+        <v>586664</v>
       </c>
       <c r="R33" t="n">
-        <v>7089749</v>
+        <v>7089845</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3811,32 +3811,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128436148</v>
+        <v>128439616</v>
       </c>
       <c r="B34" t="n">
-        <v>79735</v>
+        <v>91655</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586698</v>
+        <v>586660</v>
       </c>
       <c r="R34" t="n">
-        <v>7089750</v>
+        <v>7089907</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4102,10 +4102,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128436295</v>
+        <v>128438053</v>
       </c>
       <c r="B37" t="n">
-        <v>78782</v>
+        <v>78873</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4113,21 +4113,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586729</v>
+        <v>586682</v>
       </c>
       <c r="R37" t="n">
-        <v>7089765</v>
+        <v>7089916</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4199,32 +4199,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128437746</v>
+        <v>128436295</v>
       </c>
       <c r="B38" t="n">
-        <v>91655</v>
+        <v>78782</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586698</v>
+        <v>586729</v>
       </c>
       <c r="R38" t="n">
-        <v>7089852</v>
+        <v>7089765</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4296,32 +4296,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128436799</v>
+        <v>128437746</v>
       </c>
       <c r="B39" t="n">
-        <v>79116</v>
+        <v>91655</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586743</v>
+        <v>586698</v>
       </c>
       <c r="R39" t="n">
-        <v>7089814</v>
+        <v>7089852</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128438053</v>
+        <v>128436799</v>
       </c>
       <c r="B40" t="n">
-        <v>78873</v>
+        <v>79116</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4404,21 +4404,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586682</v>
+        <v>586743</v>
       </c>
       <c r="R40" t="n">
-        <v>7089916</v>
+        <v>7089814</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4587,10 +4587,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128446039</v>
+        <v>128437630</v>
       </c>
       <c r="B42" t="n">
-        <v>78088</v>
+        <v>78873</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4598,21 +4598,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586654</v>
+        <v>586750</v>
       </c>
       <c r="R42" t="n">
-        <v>7089830</v>
+        <v>7089861</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4684,10 +4684,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128437630</v>
+        <v>128446039</v>
       </c>
       <c r="B43" t="n">
-        <v>78873</v>
+        <v>78088</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4695,21 +4695,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586750</v>
+        <v>586654</v>
       </c>
       <c r="R43" t="n">
-        <v>7089861</v>
+        <v>7089830</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4781,10 +4781,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128437765</v>
+        <v>128439704</v>
       </c>
       <c r="B44" t="n">
-        <v>79116</v>
+        <v>92977</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4792,21 +4792,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4816,10 +4816,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586703</v>
+        <v>586666</v>
       </c>
       <c r="R44" t="n">
-        <v>7089847</v>
+        <v>7089914</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4878,32 +4878,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128439117</v>
+        <v>128439342</v>
       </c>
       <c r="B45" t="n">
-        <v>80221</v>
+        <v>91755</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>65</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586650</v>
+        <v>586657</v>
       </c>
       <c r="R45" t="n">
-        <v>7089902</v>
+        <v>7089895</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -4975,10 +4975,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128439704</v>
+        <v>128437765</v>
       </c>
       <c r="B46" t="n">
-        <v>92977</v>
+        <v>79116</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4986,21 +4986,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586666</v>
+        <v>586703</v>
       </c>
       <c r="R46" t="n">
-        <v>7089914</v>
+        <v>7089847</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5072,32 +5072,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128439342</v>
+        <v>128439117</v>
       </c>
       <c r="B47" t="n">
-        <v>91755</v>
+        <v>80221</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>65</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586657</v>
+        <v>586650</v>
       </c>
       <c r="R47" t="n">
-        <v>7089895</v>
+        <v>7089902</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5172,7 +5172,7 @@
         <v>128436111</v>
       </c>
       <c r="B48" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 38268-2025 artfynd.xlsx
+++ b/artfynd/A 38268-2025 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128439941</v>
       </c>
       <c r="B3" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>128436169</v>
       </c>
       <c r="B4" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128438321</v>
       </c>
       <c r="B5" t="n">
-        <v>78782</v>
+        <v>78786</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>128439819</v>
       </c>
       <c r="B6" t="n">
-        <v>78782</v>
+        <v>78786</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>128438180</v>
       </c>
       <c r="B7" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,32 +1289,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128440115</v>
+        <v>128440016</v>
       </c>
       <c r="B8" t="n">
-        <v>92784</v>
+        <v>78786</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586688</v>
+        <v>586691</v>
       </c>
       <c r="R8" t="n">
-        <v>7089811</v>
+        <v>7089809</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1386,32 +1386,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128440016</v>
+        <v>128440115</v>
       </c>
       <c r="B9" t="n">
-        <v>78782</v>
+        <v>92794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586691</v>
+        <v>586688</v>
       </c>
       <c r="R9" t="n">
-        <v>7089809</v>
+        <v>7089811</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1486,7 +1486,7 @@
         <v>128437589</v>
       </c>
       <c r="B10" t="n">
-        <v>91655</v>
+        <v>91665</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1580,32 +1580,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128441773</v>
+        <v>128438132</v>
       </c>
       <c r="B11" t="n">
-        <v>92784</v>
+        <v>90536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586682</v>
+        <v>586666</v>
       </c>
       <c r="R11" t="n">
-        <v>7089791</v>
+        <v>7089955</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1677,10 +1677,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128439128</v>
+        <v>128441773</v>
       </c>
       <c r="B12" t="n">
-        <v>80257</v>
+        <v>92794</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1688,21 +1688,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586657</v>
+        <v>586682</v>
       </c>
       <c r="R12" t="n">
-        <v>7089905</v>
+        <v>7089791</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1774,32 +1774,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128438132</v>
+        <v>128439128</v>
       </c>
       <c r="B13" t="n">
-        <v>90526</v>
+        <v>80261</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586666</v>
+        <v>586657</v>
       </c>
       <c r="R13" t="n">
-        <v>7089955</v>
+        <v>7089905</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128437499</v>
+        <v>128437871</v>
       </c>
       <c r="B14" t="n">
-        <v>92784</v>
+        <v>78786</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586750</v>
+        <v>586697</v>
       </c>
       <c r="R14" t="n">
-        <v>7089835</v>
+        <v>7089867</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128439671</v>
+        <v>128437499</v>
       </c>
       <c r="B15" t="n">
-        <v>91655</v>
+        <v>92794</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586664</v>
+        <v>586750</v>
       </c>
       <c r="R15" t="n">
-        <v>7089915</v>
+        <v>7089835</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2065,32 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128437871</v>
+        <v>128439671</v>
       </c>
       <c r="B16" t="n">
-        <v>78782</v>
+        <v>91665</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586697</v>
+        <v>586664</v>
       </c>
       <c r="R16" t="n">
-        <v>7089867</v>
+        <v>7089915</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2165,7 +2165,7 @@
         <v>128437645</v>
       </c>
       <c r="B17" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>128447261</v>
       </c>
       <c r="B18" t="n">
-        <v>92796</v>
+        <v>92806</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>128439814</v>
       </c>
       <c r="B19" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128439094</v>
       </c>
       <c r="B20" t="n">
-        <v>78782</v>
+        <v>78786</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>128436765</v>
       </c>
       <c r="B21" t="n">
-        <v>91459</v>
+        <v>91469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>128438427</v>
       </c>
       <c r="B22" t="n">
-        <v>92977</v>
+        <v>92989</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>128440316</v>
       </c>
       <c r="B23" t="n">
-        <v>92800</v>
+        <v>92810</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128438055</v>
       </c>
       <c r="B24" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>128437989</v>
       </c>
       <c r="B25" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3035,32 +3035,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128443168</v>
+        <v>128438141</v>
       </c>
       <c r="B26" t="n">
-        <v>92784</v>
+        <v>80225</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,7 +3073,7 @@
         <v>586666</v>
       </c>
       <c r="R26" t="n">
-        <v>7089771</v>
+        <v>7089955</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3132,32 +3132,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128438141</v>
+        <v>128443168</v>
       </c>
       <c r="B27" t="n">
-        <v>80221</v>
+        <v>92794</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3170,7 +3170,7 @@
         <v>586666</v>
       </c>
       <c r="R27" t="n">
-        <v>7089955</v>
+        <v>7089771</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3232,7 +3232,7 @@
         <v>128437686</v>
       </c>
       <c r="B28" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>128439751</v>
       </c>
       <c r="B29" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3423,32 +3423,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128438005</v>
+        <v>128436152</v>
       </c>
       <c r="B30" t="n">
-        <v>80250</v>
+        <v>79120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>586717</v>
+        <v>586699</v>
       </c>
       <c r="R30" t="n">
-        <v>7089885</v>
+        <v>7089749</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3520,32 +3520,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128436148</v>
+        <v>128438005</v>
       </c>
       <c r="B31" t="n">
-        <v>79735</v>
+        <v>80254</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3555,10 +3555,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586698</v>
+        <v>586717</v>
       </c>
       <c r="R31" t="n">
-        <v>7089750</v>
+        <v>7089885</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3617,10 +3617,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128436152</v>
+        <v>128436148</v>
       </c>
       <c r="B32" t="n">
-        <v>79116</v>
+        <v>79739</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3628,21 +3628,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586699</v>
+        <v>586698</v>
       </c>
       <c r="R32" t="n">
-        <v>7089749</v>
+        <v>7089750</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3717,7 +3717,7 @@
         <v>128439799</v>
       </c>
       <c r="B33" t="n">
-        <v>91655</v>
+        <v>91665</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>128439616</v>
       </c>
       <c r="B34" t="n">
-        <v>91655</v>
+        <v>91665</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>128437925</v>
       </c>
       <c r="B35" t="n">
-        <v>92788</v>
+        <v>92798</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>128436482</v>
       </c>
       <c r="B36" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4102,10 +4102,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128438053</v>
+        <v>128436295</v>
       </c>
       <c r="B37" t="n">
-        <v>78873</v>
+        <v>78786</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4113,21 +4113,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586682</v>
+        <v>586729</v>
       </c>
       <c r="R37" t="n">
-        <v>7089916</v>
+        <v>7089765</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4199,10 +4199,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128436295</v>
+        <v>128436799</v>
       </c>
       <c r="B38" t="n">
-        <v>78782</v>
+        <v>79120</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4210,21 +4210,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586729</v>
+        <v>586743</v>
       </c>
       <c r="R38" t="n">
-        <v>7089765</v>
+        <v>7089814</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4296,32 +4296,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128437746</v>
+        <v>128438053</v>
       </c>
       <c r="B39" t="n">
-        <v>91655</v>
+        <v>78877</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586698</v>
+        <v>586682</v>
       </c>
       <c r="R39" t="n">
-        <v>7089852</v>
+        <v>7089916</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4393,32 +4393,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128436799</v>
+        <v>128437746</v>
       </c>
       <c r="B40" t="n">
-        <v>79116</v>
+        <v>91665</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586743</v>
+        <v>586698</v>
       </c>
       <c r="R40" t="n">
-        <v>7089814</v>
+        <v>7089852</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4490,32 +4490,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128439054</v>
+        <v>128446039</v>
       </c>
       <c r="B41" t="n">
-        <v>91655</v>
+        <v>78092</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1503</v>
+        <v>6487</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586635</v>
+        <v>586654</v>
       </c>
       <c r="R41" t="n">
-        <v>7089949</v>
+        <v>7089830</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4590,7 +4590,7 @@
         <v>128437630</v>
       </c>
       <c r="B42" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4684,32 +4684,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128446039</v>
+        <v>128439054</v>
       </c>
       <c r="B43" t="n">
-        <v>78088</v>
+        <v>91665</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6487</v>
+        <v>1503</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586654</v>
+        <v>586635</v>
       </c>
       <c r="R43" t="n">
-        <v>7089830</v>
+        <v>7089949</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4781,32 +4781,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128439704</v>
+        <v>128439342</v>
       </c>
       <c r="B44" t="n">
-        <v>92977</v>
+        <v>91765</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2079</v>
+        <v>65</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4816,10 +4816,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586666</v>
+        <v>586657</v>
       </c>
       <c r="R44" t="n">
-        <v>7089914</v>
+        <v>7089895</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4878,32 +4878,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128439342</v>
+        <v>128439117</v>
       </c>
       <c r="B45" t="n">
-        <v>91755</v>
+        <v>80225</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>65</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586657</v>
+        <v>586650</v>
       </c>
       <c r="R45" t="n">
-        <v>7089895</v>
+        <v>7089902</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -4978,7 +4978,7 @@
         <v>128437765</v>
       </c>
       <c r="B46" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5072,10 +5072,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128439117</v>
+        <v>128439704</v>
       </c>
       <c r="B47" t="n">
-        <v>80221</v>
+        <v>92989</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5083,21 +5083,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586650</v>
+        <v>586666</v>
       </c>
       <c r="R47" t="n">
-        <v>7089902</v>
+        <v>7089914</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5172,7 +5172,7 @@
         <v>128436111</v>
       </c>
       <c r="B48" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 38268-2025 artfynd.xlsx
+++ b/artfynd/A 38268-2025 artfynd.xlsx
@@ -901,32 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128436169</v>
+        <v>128438321</v>
       </c>
       <c r="B4" t="n">
-        <v>92794</v>
+        <v>78786</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586711</v>
+        <v>586605</v>
       </c>
       <c r="R4" t="n">
-        <v>7089755</v>
+        <v>7090026</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -998,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128438321</v>
+        <v>128436169</v>
       </c>
       <c r="B5" t="n">
-        <v>78786</v>
+        <v>92794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586605</v>
+        <v>586711</v>
       </c>
       <c r="R5" t="n">
-        <v>7090026</v>
+        <v>7089755</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1289,32 +1289,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128440016</v>
+        <v>128440115</v>
       </c>
       <c r="B8" t="n">
-        <v>78786</v>
+        <v>92794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586691</v>
+        <v>586688</v>
       </c>
       <c r="R8" t="n">
-        <v>7089809</v>
+        <v>7089811</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1386,32 +1386,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128440115</v>
+        <v>128440016</v>
       </c>
       <c r="B9" t="n">
-        <v>92794</v>
+        <v>78786</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586688</v>
+        <v>586691</v>
       </c>
       <c r="R9" t="n">
-        <v>7089811</v>
+        <v>7089809</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1580,32 +1580,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128438132</v>
+        <v>128441773</v>
       </c>
       <c r="B11" t="n">
-        <v>90536</v>
+        <v>92794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586666</v>
+        <v>586682</v>
       </c>
       <c r="R11" t="n">
-        <v>7089955</v>
+        <v>7089791</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1677,32 +1677,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128441773</v>
+        <v>128438132</v>
       </c>
       <c r="B12" t="n">
-        <v>92794</v>
+        <v>90536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586682</v>
+        <v>586666</v>
       </c>
       <c r="R12" t="n">
-        <v>7089791</v>
+        <v>7089955</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128437871</v>
+        <v>128439671</v>
       </c>
       <c r="B14" t="n">
-        <v>78786</v>
+        <v>91665</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586697</v>
+        <v>586664</v>
       </c>
       <c r="R14" t="n">
-        <v>7089867</v>
+        <v>7089915</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128437499</v>
+        <v>128437871</v>
       </c>
       <c r="B15" t="n">
-        <v>92794</v>
+        <v>78786</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586750</v>
+        <v>586697</v>
       </c>
       <c r="R15" t="n">
-        <v>7089835</v>
+        <v>7089867</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2065,32 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128439671</v>
+        <v>128437499</v>
       </c>
       <c r="B16" t="n">
-        <v>91665</v>
+        <v>92794</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586664</v>
+        <v>586750</v>
       </c>
       <c r="R16" t="n">
-        <v>7089915</v>
+        <v>7089835</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2162,32 +2162,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128437645</v>
+        <v>128447261</v>
       </c>
       <c r="B17" t="n">
-        <v>79739</v>
+        <v>92806</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586746</v>
+        <v>586663</v>
       </c>
       <c r="R17" t="n">
-        <v>7089860</v>
+        <v>7089829</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2259,32 +2259,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128447261</v>
+        <v>128437645</v>
       </c>
       <c r="B18" t="n">
-        <v>92806</v>
+        <v>79739</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586663</v>
+        <v>586746</v>
       </c>
       <c r="R18" t="n">
-        <v>7089829</v>
+        <v>7089860</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2841,32 +2841,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128438055</v>
+        <v>128437989</v>
       </c>
       <c r="B24" t="n">
-        <v>92794</v>
+        <v>80225</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586682</v>
+        <v>586701</v>
       </c>
       <c r="R24" t="n">
-        <v>7089917</v>
+        <v>7089891</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2938,32 +2938,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128437989</v>
+        <v>128438055</v>
       </c>
       <c r="B25" t="n">
-        <v>80225</v>
+        <v>92794</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586701</v>
+        <v>586682</v>
       </c>
       <c r="R25" t="n">
-        <v>7089891</v>
+        <v>7089917</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3035,32 +3035,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128438141</v>
+        <v>128443168</v>
       </c>
       <c r="B26" t="n">
-        <v>80225</v>
+        <v>92794</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,7 +3073,7 @@
         <v>586666</v>
       </c>
       <c r="R26" t="n">
-        <v>7089955</v>
+        <v>7089771</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3132,32 +3132,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128443168</v>
+        <v>128438141</v>
       </c>
       <c r="B27" t="n">
-        <v>92794</v>
+        <v>80225</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3170,7 +3170,7 @@
         <v>586666</v>
       </c>
       <c r="R27" t="n">
-        <v>7089771</v>
+        <v>7089955</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3326,32 +3326,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128439751</v>
+        <v>128439799</v>
       </c>
       <c r="B29" t="n">
-        <v>79739</v>
+        <v>91665</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586681</v>
+        <v>586664</v>
       </c>
       <c r="R29" t="n">
-        <v>7089872</v>
+        <v>7089845</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3423,32 +3423,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128436152</v>
+        <v>128439616</v>
       </c>
       <c r="B30" t="n">
-        <v>79120</v>
+        <v>91665</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>586699</v>
+        <v>586660</v>
       </c>
       <c r="R30" t="n">
-        <v>7089749</v>
+        <v>7089907</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3520,32 +3520,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128438005</v>
+        <v>128439751</v>
       </c>
       <c r="B31" t="n">
-        <v>80254</v>
+        <v>79739</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3555,10 +3555,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586717</v>
+        <v>586681</v>
       </c>
       <c r="R31" t="n">
-        <v>7089885</v>
+        <v>7089872</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3617,10 +3617,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128436148</v>
+        <v>128436152</v>
       </c>
       <c r="B32" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3628,21 +3628,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586698</v>
+        <v>586699</v>
       </c>
       <c r="R32" t="n">
-        <v>7089750</v>
+        <v>7089749</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3714,32 +3714,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128439799</v>
+        <v>128438005</v>
       </c>
       <c r="B33" t="n">
-        <v>91665</v>
+        <v>80254</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1503</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586664</v>
+        <v>586717</v>
       </c>
       <c r="R33" t="n">
-        <v>7089845</v>
+        <v>7089885</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3811,32 +3811,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128439616</v>
+        <v>128436148</v>
       </c>
       <c r="B34" t="n">
-        <v>91665</v>
+        <v>79739</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586660</v>
+        <v>586698</v>
       </c>
       <c r="R34" t="n">
-        <v>7089907</v>
+        <v>7089750</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4199,32 +4199,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128436799</v>
+        <v>128437746</v>
       </c>
       <c r="B38" t="n">
-        <v>79120</v>
+        <v>91665</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586743</v>
+        <v>586698</v>
       </c>
       <c r="R38" t="n">
-        <v>7089814</v>
+        <v>7089852</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4296,10 +4296,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128438053</v>
+        <v>128436799</v>
       </c>
       <c r="B39" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4307,21 +4307,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586682</v>
+        <v>586743</v>
       </c>
       <c r="R39" t="n">
-        <v>7089916</v>
+        <v>7089814</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4393,32 +4393,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128437746</v>
+        <v>128438053</v>
       </c>
       <c r="B40" t="n">
-        <v>91665</v>
+        <v>78877</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586698</v>
+        <v>586682</v>
       </c>
       <c r="R40" t="n">
-        <v>7089852</v>
+        <v>7089916</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4587,32 +4587,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128437630</v>
+        <v>128439054</v>
       </c>
       <c r="B42" t="n">
-        <v>78877</v>
+        <v>91665</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586750</v>
+        <v>586635</v>
       </c>
       <c r="R42" t="n">
-        <v>7089861</v>
+        <v>7089949</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4684,32 +4684,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128439054</v>
+        <v>128437630</v>
       </c>
       <c r="B43" t="n">
-        <v>91665</v>
+        <v>78877</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586635</v>
+        <v>586750</v>
       </c>
       <c r="R43" t="n">
-        <v>7089949</v>
+        <v>7089861</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4781,32 +4781,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128439342</v>
+        <v>128439704</v>
       </c>
       <c r="B44" t="n">
-        <v>91765</v>
+        <v>92989</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4816,10 +4816,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586657</v>
+        <v>586666</v>
       </c>
       <c r="R44" t="n">
-        <v>7089895</v>
+        <v>7089914</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4878,32 +4878,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128439117</v>
+        <v>128439342</v>
       </c>
       <c r="B45" t="n">
-        <v>80225</v>
+        <v>91765</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>65</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586650</v>
+        <v>586657</v>
       </c>
       <c r="R45" t="n">
-        <v>7089902</v>
+        <v>7089895</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5072,10 +5072,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128439704</v>
+        <v>128439117</v>
       </c>
       <c r="B47" t="n">
-        <v>92989</v>
+        <v>80225</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5083,21 +5083,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586666</v>
+        <v>586650</v>
       </c>
       <c r="R47" t="n">
-        <v>7089914</v>
+        <v>7089902</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>

--- a/artfynd/A 38268-2025 artfynd.xlsx
+++ b/artfynd/A 38268-2025 artfynd.xlsx
@@ -4490,32 +4490,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128446039</v>
+        <v>128439054</v>
       </c>
       <c r="B41" t="n">
-        <v>78092</v>
+        <v>91665</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6487</v>
+        <v>1503</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586654</v>
+        <v>586635</v>
       </c>
       <c r="R41" t="n">
-        <v>7089830</v>
+        <v>7089949</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4587,32 +4587,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128439054</v>
+        <v>128437630</v>
       </c>
       <c r="B42" t="n">
-        <v>91665</v>
+        <v>78877</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586635</v>
+        <v>586750</v>
       </c>
       <c r="R42" t="n">
-        <v>7089949</v>
+        <v>7089861</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4684,10 +4684,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128437630</v>
+        <v>128446039</v>
       </c>
       <c r="B43" t="n">
-        <v>78877</v>
+        <v>78092</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4695,21 +4695,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586750</v>
+        <v>586654</v>
       </c>
       <c r="R43" t="n">
-        <v>7089861</v>
+        <v>7089830</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4781,10 +4781,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128439704</v>
+        <v>128437765</v>
       </c>
       <c r="B44" t="n">
-        <v>92989</v>
+        <v>79120</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4792,21 +4792,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4816,10 +4816,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586666</v>
+        <v>586703</v>
       </c>
       <c r="R44" t="n">
-        <v>7089914</v>
+        <v>7089847</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4878,32 +4878,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128439342</v>
+        <v>128439117</v>
       </c>
       <c r="B45" t="n">
-        <v>91765</v>
+        <v>80225</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>65</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586657</v>
+        <v>586650</v>
       </c>
       <c r="R45" t="n">
-        <v>7089895</v>
+        <v>7089902</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -4975,10 +4975,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128437765</v>
+        <v>128439704</v>
       </c>
       <c r="B46" t="n">
-        <v>79120</v>
+        <v>92989</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4986,21 +4986,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586703</v>
+        <v>586666</v>
       </c>
       <c r="R46" t="n">
-        <v>7089847</v>
+        <v>7089914</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5072,32 +5072,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128439117</v>
+        <v>128439342</v>
       </c>
       <c r="B47" t="n">
-        <v>80225</v>
+        <v>91765</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>65</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586650</v>
+        <v>586657</v>
       </c>
       <c r="R47" t="n">
-        <v>7089902</v>
+        <v>7089895</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>

--- a/artfynd/A 38268-2025 artfynd.xlsx
+++ b/artfynd/A 38268-2025 artfynd.xlsx
@@ -901,32 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128438321</v>
+        <v>128436169</v>
       </c>
       <c r="B4" t="n">
-        <v>78786</v>
+        <v>92794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586605</v>
+        <v>586711</v>
       </c>
       <c r="R4" t="n">
-        <v>7090026</v>
+        <v>7089755</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -998,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128436169</v>
+        <v>128438321</v>
       </c>
       <c r="B5" t="n">
-        <v>92794</v>
+        <v>78786</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586711</v>
+        <v>586605</v>
       </c>
       <c r="R5" t="n">
-        <v>7089755</v>
+        <v>7090026</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1580,32 +1580,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128441773</v>
+        <v>128438132</v>
       </c>
       <c r="B11" t="n">
-        <v>92794</v>
+        <v>90536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586682</v>
+        <v>586666</v>
       </c>
       <c r="R11" t="n">
-        <v>7089791</v>
+        <v>7089955</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1677,32 +1677,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128438132</v>
+        <v>128439128</v>
       </c>
       <c r="B12" t="n">
-        <v>90536</v>
+        <v>80261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586666</v>
+        <v>586657</v>
       </c>
       <c r="R12" t="n">
-        <v>7089955</v>
+        <v>7089905</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1774,10 +1774,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128439128</v>
+        <v>128441773</v>
       </c>
       <c r="B13" t="n">
-        <v>80261</v>
+        <v>92794</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1785,21 +1785,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586657</v>
+        <v>586682</v>
       </c>
       <c r="R13" t="n">
-        <v>7089905</v>
+        <v>7089791</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128439671</v>
+        <v>128437499</v>
       </c>
       <c r="B14" t="n">
-        <v>91665</v>
+        <v>92794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586664</v>
+        <v>586750</v>
       </c>
       <c r="R14" t="n">
-        <v>7089915</v>
+        <v>7089835</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2065,32 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128437499</v>
+        <v>128439671</v>
       </c>
       <c r="B16" t="n">
-        <v>92794</v>
+        <v>91665</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586750</v>
+        <v>586664</v>
       </c>
       <c r="R16" t="n">
-        <v>7089835</v>
+        <v>7089915</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -3326,32 +3326,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128439799</v>
+        <v>128438005</v>
       </c>
       <c r="B29" t="n">
-        <v>91665</v>
+        <v>80254</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1503</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586664</v>
+        <v>586717</v>
       </c>
       <c r="R29" t="n">
-        <v>7089845</v>
+        <v>7089885</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3423,7 +3423,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128439616</v>
+        <v>128439799</v>
       </c>
       <c r="B30" t="n">
         <v>91665</v>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>586660</v>
+        <v>586664</v>
       </c>
       <c r="R30" t="n">
-        <v>7089907</v>
+        <v>7089845</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3520,32 +3520,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128439751</v>
+        <v>128439616</v>
       </c>
       <c r="B31" t="n">
-        <v>79739</v>
+        <v>91665</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3555,10 +3555,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586681</v>
+        <v>586660</v>
       </c>
       <c r="R31" t="n">
-        <v>7089872</v>
+        <v>7089907</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3617,10 +3617,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128436152</v>
+        <v>128439751</v>
       </c>
       <c r="B32" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3628,21 +3628,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586699</v>
+        <v>586681</v>
       </c>
       <c r="R32" t="n">
-        <v>7089749</v>
+        <v>7089872</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3714,32 +3714,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128438005</v>
+        <v>128436148</v>
       </c>
       <c r="B33" t="n">
-        <v>80254</v>
+        <v>79739</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586717</v>
+        <v>586698</v>
       </c>
       <c r="R33" t="n">
-        <v>7089885</v>
+        <v>7089750</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128436148</v>
+        <v>128436152</v>
       </c>
       <c r="B34" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3822,21 +3822,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586698</v>
+        <v>586699</v>
       </c>
       <c r="R34" t="n">
-        <v>7089750</v>
+        <v>7089749</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4102,10 +4102,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128436295</v>
+        <v>128436799</v>
       </c>
       <c r="B37" t="n">
-        <v>78786</v>
+        <v>79120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4113,21 +4113,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586729</v>
+        <v>586743</v>
       </c>
       <c r="R37" t="n">
-        <v>7089765</v>
+        <v>7089814</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4199,32 +4199,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128437746</v>
+        <v>128436295</v>
       </c>
       <c r="B38" t="n">
-        <v>91665</v>
+        <v>78786</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586698</v>
+        <v>586729</v>
       </c>
       <c r="R38" t="n">
-        <v>7089852</v>
+        <v>7089765</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4296,32 +4296,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128436799</v>
+        <v>128437746</v>
       </c>
       <c r="B39" t="n">
-        <v>79120</v>
+        <v>91665</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586743</v>
+        <v>586698</v>
       </c>
       <c r="R39" t="n">
-        <v>7089814</v>
+        <v>7089852</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4781,32 +4781,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128437765</v>
+        <v>128439342</v>
       </c>
       <c r="B44" t="n">
-        <v>79120</v>
+        <v>91765</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4816,10 +4816,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586703</v>
+        <v>586657</v>
       </c>
       <c r="R44" t="n">
-        <v>7089847</v>
+        <v>7089895</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4878,10 +4878,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128439117</v>
+        <v>128437765</v>
       </c>
       <c r="B45" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4889,21 +4889,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586650</v>
+        <v>586703</v>
       </c>
       <c r="R45" t="n">
-        <v>7089902</v>
+        <v>7089847</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -4975,10 +4975,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128439704</v>
+        <v>128439117</v>
       </c>
       <c r="B46" t="n">
-        <v>92989</v>
+        <v>80225</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4986,21 +4986,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586666</v>
+        <v>586650</v>
       </c>
       <c r="R46" t="n">
-        <v>7089914</v>
+        <v>7089902</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5072,32 +5072,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128439342</v>
+        <v>128439704</v>
       </c>
       <c r="B47" t="n">
-        <v>91765</v>
+        <v>92989</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586657</v>
+        <v>586666</v>
       </c>
       <c r="R47" t="n">
-        <v>7089895</v>
+        <v>7089914</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5172,7 +5172,7 @@
         <v>128436111</v>
       </c>
       <c r="B48" t="n">
-        <v>92820</v>
+        <v>92824</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 38268-2025 artfynd.xlsx
+++ b/artfynd/A 38268-2025 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128439941</v>
       </c>
       <c r="B3" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,32 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128436169</v>
+        <v>128438321</v>
       </c>
       <c r="B4" t="n">
-        <v>92794</v>
+        <v>78790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586711</v>
+        <v>586605</v>
       </c>
       <c r="R4" t="n">
-        <v>7089755</v>
+        <v>7090026</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -998,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128438321</v>
+        <v>128436169</v>
       </c>
       <c r="B5" t="n">
-        <v>78786</v>
+        <v>92798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586605</v>
+        <v>586711</v>
       </c>
       <c r="R5" t="n">
-        <v>7090026</v>
+        <v>7089755</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128439819</v>
+        <v>128438180</v>
       </c>
       <c r="B6" t="n">
-        <v>78786</v>
+        <v>80229</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586673</v>
+        <v>586656</v>
       </c>
       <c r="R6" t="n">
-        <v>7089842</v>
+        <v>7090016</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128438180</v>
+        <v>128439819</v>
       </c>
       <c r="B7" t="n">
-        <v>80225</v>
+        <v>78790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,21 +1203,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586656</v>
+        <v>586673</v>
       </c>
       <c r="R7" t="n">
-        <v>7090016</v>
+        <v>7089842</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1289,32 +1289,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128440115</v>
+        <v>128440016</v>
       </c>
       <c r="B8" t="n">
-        <v>92794</v>
+        <v>78790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586688</v>
+        <v>586691</v>
       </c>
       <c r="R8" t="n">
-        <v>7089811</v>
+        <v>7089809</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1386,32 +1386,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128440016</v>
+        <v>128437589</v>
       </c>
       <c r="B9" t="n">
-        <v>78786</v>
+        <v>91669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586691</v>
+        <v>586739</v>
       </c>
       <c r="R9" t="n">
-        <v>7089809</v>
+        <v>7089865</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1483,32 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128437589</v>
+        <v>128440115</v>
       </c>
       <c r="B10" t="n">
-        <v>91665</v>
+        <v>92798</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586739</v>
+        <v>586688</v>
       </c>
       <c r="R10" t="n">
-        <v>7089865</v>
+        <v>7089811</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1583,7 +1583,7 @@
         <v>128438132</v>
       </c>
       <c r="B11" t="n">
-        <v>90536</v>
+        <v>90540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1677,10 +1677,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128439128</v>
+        <v>128441773</v>
       </c>
       <c r="B12" t="n">
-        <v>80261</v>
+        <v>92798</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1688,21 +1688,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586657</v>
+        <v>586682</v>
       </c>
       <c r="R12" t="n">
-        <v>7089905</v>
+        <v>7089791</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1774,10 +1774,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128441773</v>
+        <v>128439128</v>
       </c>
       <c r="B13" t="n">
-        <v>92794</v>
+        <v>80265</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1785,21 +1785,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586682</v>
+        <v>586657</v>
       </c>
       <c r="R13" t="n">
-        <v>7089791</v>
+        <v>7089905</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128437499</v>
+        <v>128439671</v>
       </c>
       <c r="B14" t="n">
-        <v>92794</v>
+        <v>91669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586750</v>
+        <v>586664</v>
       </c>
       <c r="R14" t="n">
-        <v>7089835</v>
+        <v>7089915</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1971,7 +1971,7 @@
         <v>128437871</v>
       </c>
       <c r="B15" t="n">
-        <v>78786</v>
+        <v>78790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,32 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128439671</v>
+        <v>128437499</v>
       </c>
       <c r="B16" t="n">
-        <v>91665</v>
+        <v>92798</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586664</v>
+        <v>586750</v>
       </c>
       <c r="R16" t="n">
-        <v>7089915</v>
+        <v>7089835</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2162,32 +2162,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128447261</v>
+        <v>128437645</v>
       </c>
       <c r="B17" t="n">
-        <v>92806</v>
+        <v>79743</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586663</v>
+        <v>586746</v>
       </c>
       <c r="R17" t="n">
-        <v>7089829</v>
+        <v>7089860</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2259,32 +2259,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128437645</v>
+        <v>128447261</v>
       </c>
       <c r="B18" t="n">
-        <v>79739</v>
+        <v>92810</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586746</v>
+        <v>586663</v>
       </c>
       <c r="R18" t="n">
-        <v>7089860</v>
+        <v>7089829</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2359,7 +2359,7 @@
         <v>128439814</v>
       </c>
       <c r="B19" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128439094</v>
       </c>
       <c r="B20" t="n">
-        <v>78786</v>
+        <v>78790</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>128436765</v>
       </c>
       <c r="B21" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>128438427</v>
       </c>
       <c r="B22" t="n">
-        <v>92989</v>
+        <v>92993</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>128440316</v>
       </c>
       <c r="B23" t="n">
-        <v>92810</v>
+        <v>92814</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128437989</v>
       </c>
       <c r="B24" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>128438055</v>
       </c>
       <c r="B25" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3035,32 +3035,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128443168</v>
+        <v>128438141</v>
       </c>
       <c r="B26" t="n">
-        <v>92794</v>
+        <v>80229</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,7 +3073,7 @@
         <v>586666</v>
       </c>
       <c r="R26" t="n">
-        <v>7089771</v>
+        <v>7089955</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128438141</v>
+        <v>128437686</v>
       </c>
       <c r="B27" t="n">
-        <v>80225</v>
+        <v>79743</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3143,21 +3143,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3167,10 +3167,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586666</v>
+        <v>586741</v>
       </c>
       <c r="R27" t="n">
-        <v>7089955</v>
+        <v>7089870</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3229,32 +3229,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128437686</v>
+        <v>128443168</v>
       </c>
       <c r="B28" t="n">
-        <v>79739</v>
+        <v>92798</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586741</v>
+        <v>586666</v>
       </c>
       <c r="R28" t="n">
-        <v>7089870</v>
+        <v>7089771</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3326,32 +3326,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128438005</v>
+        <v>128439799</v>
       </c>
       <c r="B29" t="n">
-        <v>80254</v>
+        <v>91669</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>1503</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586717</v>
+        <v>586664</v>
       </c>
       <c r="R29" t="n">
-        <v>7089885</v>
+        <v>7089845</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3423,10 +3423,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128439799</v>
+        <v>128439616</v>
       </c>
       <c r="B30" t="n">
-        <v>91665</v>
+        <v>91669</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>586664</v>
+        <v>586660</v>
       </c>
       <c r="R30" t="n">
-        <v>7089845</v>
+        <v>7089907</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3520,32 +3520,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128439616</v>
+        <v>128436152</v>
       </c>
       <c r="B31" t="n">
-        <v>91665</v>
+        <v>79124</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3555,10 +3555,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586660</v>
+        <v>586699</v>
       </c>
       <c r="R31" t="n">
-        <v>7089907</v>
+        <v>7089749</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3620,7 +3620,7 @@
         <v>128439751</v>
       </c>
       <c r="B32" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3714,32 +3714,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128436148</v>
+        <v>128438005</v>
       </c>
       <c r="B33" t="n">
-        <v>79739</v>
+        <v>80258</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586698</v>
+        <v>586717</v>
       </c>
       <c r="R33" t="n">
-        <v>7089750</v>
+        <v>7089885</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128436152</v>
+        <v>128436148</v>
       </c>
       <c r="B34" t="n">
-        <v>79120</v>
+        <v>79743</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3822,21 +3822,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586699</v>
+        <v>586698</v>
       </c>
       <c r="R34" t="n">
-        <v>7089749</v>
+        <v>7089750</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3911,7 +3911,7 @@
         <v>128437925</v>
       </c>
       <c r="B35" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>128436482</v>
       </c>
       <c r="B36" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4102,10 +4102,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128436799</v>
+        <v>128438053</v>
       </c>
       <c r="B37" t="n">
-        <v>79120</v>
+        <v>78881</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4113,21 +4113,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586743</v>
+        <v>586682</v>
       </c>
       <c r="R37" t="n">
-        <v>7089814</v>
+        <v>7089916</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4202,7 +4202,7 @@
         <v>128436295</v>
       </c>
       <c r="B38" t="n">
-        <v>78786</v>
+        <v>78790</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>128437746</v>
       </c>
       <c r="B39" t="n">
-        <v>91665</v>
+        <v>91669</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128438053</v>
+        <v>128436799</v>
       </c>
       <c r="B40" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4404,21 +4404,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586682</v>
+        <v>586743</v>
       </c>
       <c r="R40" t="n">
-        <v>7089916</v>
+        <v>7089814</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4493,7 +4493,7 @@
         <v>128439054</v>
       </c>
       <c r="B41" t="n">
-        <v>91665</v>
+        <v>91669</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>128437630</v>
       </c>
       <c r="B42" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>128446039</v>
       </c>
       <c r="B43" t="n">
-        <v>78092</v>
+        <v>78096</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>128439342</v>
       </c>
       <c r="B44" t="n">
-        <v>91765</v>
+        <v>91769</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4878,10 +4878,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128437765</v>
+        <v>128439704</v>
       </c>
       <c r="B45" t="n">
-        <v>79120</v>
+        <v>92993</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4889,21 +4889,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586703</v>
+        <v>586666</v>
       </c>
       <c r="R45" t="n">
-        <v>7089847</v>
+        <v>7089914</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -4975,10 +4975,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128439117</v>
+        <v>128437765</v>
       </c>
       <c r="B46" t="n">
-        <v>80225</v>
+        <v>79124</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4986,21 +4986,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586650</v>
+        <v>586703</v>
       </c>
       <c r="R46" t="n">
-        <v>7089902</v>
+        <v>7089847</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5072,10 +5072,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128439704</v>
+        <v>128439117</v>
       </c>
       <c r="B47" t="n">
-        <v>92989</v>
+        <v>80229</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5083,21 +5083,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586666</v>
+        <v>586650</v>
       </c>
       <c r="R47" t="n">
-        <v>7089914</v>
+        <v>7089902</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>

--- a/artfynd/A 38268-2025 artfynd.xlsx
+++ b/artfynd/A 38268-2025 artfynd.xlsx
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128438180</v>
+        <v>128439819</v>
       </c>
       <c r="B6" t="n">
-        <v>80229</v>
+        <v>78790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586656</v>
+        <v>586673</v>
       </c>
       <c r="R6" t="n">
-        <v>7090016</v>
+        <v>7089842</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128439819</v>
+        <v>128438180</v>
       </c>
       <c r="B7" t="n">
-        <v>78790</v>
+        <v>80229</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,21 +1203,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586673</v>
+        <v>586656</v>
       </c>
       <c r="R7" t="n">
-        <v>7089842</v>
+        <v>7090016</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -3035,32 +3035,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128438141</v>
+        <v>128443168</v>
       </c>
       <c r="B26" t="n">
-        <v>80229</v>
+        <v>92798</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,7 +3073,7 @@
         <v>586666</v>
       </c>
       <c r="R26" t="n">
-        <v>7089955</v>
+        <v>7089771</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128437686</v>
+        <v>128438141</v>
       </c>
       <c r="B27" t="n">
-        <v>79743</v>
+        <v>80229</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3143,21 +3143,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3167,10 +3167,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586741</v>
+        <v>586666</v>
       </c>
       <c r="R27" t="n">
-        <v>7089870</v>
+        <v>7089955</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3229,32 +3229,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128443168</v>
+        <v>128437686</v>
       </c>
       <c r="B28" t="n">
-        <v>92798</v>
+        <v>79743</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586666</v>
+        <v>586741</v>
       </c>
       <c r="R28" t="n">
-        <v>7089771</v>
+        <v>7089870</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -4102,10 +4102,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128438053</v>
+        <v>128436295</v>
       </c>
       <c r="B37" t="n">
-        <v>78881</v>
+        <v>78790</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4113,21 +4113,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586682</v>
+        <v>586729</v>
       </c>
       <c r="R37" t="n">
-        <v>7089916</v>
+        <v>7089765</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4199,32 +4199,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128436295</v>
+        <v>128437746</v>
       </c>
       <c r="B38" t="n">
-        <v>78790</v>
+        <v>91669</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586729</v>
+        <v>586698</v>
       </c>
       <c r="R38" t="n">
-        <v>7089765</v>
+        <v>7089852</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4296,32 +4296,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128437746</v>
+        <v>128436799</v>
       </c>
       <c r="B39" t="n">
-        <v>91669</v>
+        <v>79124</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586698</v>
+        <v>586743</v>
       </c>
       <c r="R39" t="n">
-        <v>7089852</v>
+        <v>7089814</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128436799</v>
+        <v>128438053</v>
       </c>
       <c r="B40" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4404,21 +4404,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586743</v>
+        <v>586682</v>
       </c>
       <c r="R40" t="n">
-        <v>7089814</v>
+        <v>7089916</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>

--- a/artfynd/A 38268-2025 artfynd.xlsx
+++ b/artfynd/A 38268-2025 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128439941</v>
       </c>
       <c r="B3" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,32 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128438321</v>
+        <v>128436169</v>
       </c>
       <c r="B4" t="n">
-        <v>78790</v>
+        <v>92803</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586605</v>
+        <v>586711</v>
       </c>
       <c r="R4" t="n">
-        <v>7090026</v>
+        <v>7089755</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -998,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128436169</v>
+        <v>128438321</v>
       </c>
       <c r="B5" t="n">
-        <v>92798</v>
+        <v>78695</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586711</v>
+        <v>586605</v>
       </c>
       <c r="R5" t="n">
-        <v>7089755</v>
+        <v>7090026</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1098,7 +1098,7 @@
         <v>128439819</v>
       </c>
       <c r="B6" t="n">
-        <v>78790</v>
+        <v>78695</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>128438180</v>
       </c>
       <c r="B7" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128440016</v>
       </c>
       <c r="B8" t="n">
-        <v>78790</v>
+        <v>78695</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>128437589</v>
       </c>
       <c r="B9" t="n">
-        <v>91669</v>
+        <v>91674</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128440115</v>
       </c>
       <c r="B10" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>128438132</v>
       </c>
       <c r="B11" t="n">
-        <v>90540</v>
+        <v>90545</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1677,10 +1677,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128441773</v>
+        <v>128439128</v>
       </c>
       <c r="B12" t="n">
-        <v>92798</v>
+        <v>80170</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1688,21 +1688,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586682</v>
+        <v>586657</v>
       </c>
       <c r="R12" t="n">
-        <v>7089791</v>
+        <v>7089905</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1774,10 +1774,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128439128</v>
+        <v>128441773</v>
       </c>
       <c r="B13" t="n">
-        <v>80265</v>
+        <v>92803</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1785,21 +1785,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586657</v>
+        <v>586682</v>
       </c>
       <c r="R13" t="n">
-        <v>7089905</v>
+        <v>7089791</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1874,7 +1874,7 @@
         <v>128439671</v>
       </c>
       <c r="B14" t="n">
-        <v>91669</v>
+        <v>91674</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>128437871</v>
       </c>
       <c r="B15" t="n">
-        <v>78790</v>
+        <v>78695</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>128437499</v>
       </c>
       <c r="B16" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,32 +2162,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128437645</v>
+        <v>128447261</v>
       </c>
       <c r="B17" t="n">
-        <v>79743</v>
+        <v>92815</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586746</v>
+        <v>586663</v>
       </c>
       <c r="R17" t="n">
-        <v>7089860</v>
+        <v>7089829</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2259,32 +2259,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128447261</v>
+        <v>128437645</v>
       </c>
       <c r="B18" t="n">
-        <v>92810</v>
+        <v>79648</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586663</v>
+        <v>586746</v>
       </c>
       <c r="R18" t="n">
-        <v>7089829</v>
+        <v>7089860</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2359,7 +2359,7 @@
         <v>128439814</v>
       </c>
       <c r="B19" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2453,32 +2453,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128439094</v>
+        <v>128436765</v>
       </c>
       <c r="B20" t="n">
-        <v>78790</v>
+        <v>91478</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586622</v>
+        <v>586735</v>
       </c>
       <c r="R20" t="n">
-        <v>7089926</v>
+        <v>7089818</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2550,32 +2550,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128436765</v>
+        <v>128439094</v>
       </c>
       <c r="B21" t="n">
-        <v>91473</v>
+        <v>78695</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586735</v>
+        <v>586622</v>
       </c>
       <c r="R21" t="n">
-        <v>7089818</v>
+        <v>7089926</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2650,7 +2650,7 @@
         <v>128438427</v>
       </c>
       <c r="B22" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>128440316</v>
       </c>
       <c r="B23" t="n">
-        <v>92814</v>
+        <v>92819</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2841,32 +2841,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128437989</v>
+        <v>128438055</v>
       </c>
       <c r="B24" t="n">
-        <v>80229</v>
+        <v>92803</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586701</v>
+        <v>586682</v>
       </c>
       <c r="R24" t="n">
-        <v>7089891</v>
+        <v>7089917</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2938,32 +2938,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128438055</v>
+        <v>128437989</v>
       </c>
       <c r="B25" t="n">
-        <v>92798</v>
+        <v>80134</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586682</v>
+        <v>586701</v>
       </c>
       <c r="R25" t="n">
-        <v>7089917</v>
+        <v>7089891</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3038,7 +3038,7 @@
         <v>128443168</v>
       </c>
       <c r="B26" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>128438141</v>
       </c>
       <c r="B27" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>128437686</v>
       </c>
       <c r="B28" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>128439799</v>
       </c>
       <c r="B29" t="n">
-        <v>91669</v>
+        <v>91674</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>128439616</v>
       </c>
       <c r="B30" t="n">
-        <v>91669</v>
+        <v>91674</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128436152</v>
+        <v>128439751</v>
       </c>
       <c r="B31" t="n">
-        <v>79124</v>
+        <v>79648</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3531,21 +3531,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3555,10 +3555,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586699</v>
+        <v>586681</v>
       </c>
       <c r="R31" t="n">
-        <v>7089749</v>
+        <v>7089872</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3617,10 +3617,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128439751</v>
+        <v>128436152</v>
       </c>
       <c r="B32" t="n">
-        <v>79743</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3628,21 +3628,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586681</v>
+        <v>586699</v>
       </c>
       <c r="R32" t="n">
-        <v>7089872</v>
+        <v>7089749</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3717,7 +3717,7 @@
         <v>128438005</v>
       </c>
       <c r="B33" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>128436148</v>
       </c>
       <c r="B34" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>128437925</v>
       </c>
       <c r="B35" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>128436482</v>
       </c>
       <c r="B36" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>128436295</v>
       </c>
       <c r="B37" t="n">
-        <v>78790</v>
+        <v>78695</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>128437746</v>
       </c>
       <c r="B38" t="n">
-        <v>91669</v>
+        <v>91674</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>128436799</v>
       </c>
       <c r="B39" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>128438053</v>
       </c>
       <c r="B40" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>128439054</v>
       </c>
       <c r="B41" t="n">
-        <v>91669</v>
+        <v>91674</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>128437630</v>
       </c>
       <c r="B42" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>128446039</v>
       </c>
       <c r="B43" t="n">
-        <v>78096</v>
+        <v>78037</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>128439342</v>
       </c>
       <c r="B44" t="n">
-        <v>91769</v>
+        <v>91774</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>128439704</v>
       </c>
       <c r="B45" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>128437765</v>
       </c>
       <c r="B46" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>128439117</v>
       </c>
       <c r="B47" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>128436111</v>
       </c>
       <c r="B48" t="n">
-        <v>92824</v>
+        <v>92829</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 38268-2025 artfynd.xlsx
+++ b/artfynd/A 38268-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75247200</v>
+        <v>128439342</v>
       </c>
       <c r="B2" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nybäcksberget, Ång</t>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586571.9404938343</v>
+        <v>586657</v>
       </c>
       <c r="R2" t="n">
-        <v>7089894.799416844</v>
+        <v>7089895</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-07-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-07-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,43 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>brandpåverkad tallskog på moränkulle</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal tallåga</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128439941</v>
+        <v>128436295</v>
       </c>
       <c r="B3" t="n">
-        <v>78786</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586701</v>
+        <v>586729</v>
       </c>
       <c r="R3" t="n">
-        <v>7089852</v>
+        <v>7089765</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -901,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128438321</v>
+        <v>128436683</v>
       </c>
       <c r="B4" t="n">
-        <v>78695</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -936,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586605</v>
+        <v>586760</v>
       </c>
       <c r="R4" t="n">
-        <v>7090026</v>
+        <v>7089811</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -998,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128436169</v>
+        <v>128437417</v>
       </c>
       <c r="B5" t="n">
-        <v>92805</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586711</v>
+        <v>586757</v>
       </c>
       <c r="R5" t="n">
-        <v>7089755</v>
+        <v>7089809</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1095,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128438180</v>
+        <v>128437871</v>
       </c>
       <c r="B6" t="n">
-        <v>80134</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586656</v>
+        <v>586697</v>
       </c>
       <c r="R6" t="n">
-        <v>7090016</v>
+        <v>7089867</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1192,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128439819</v>
+        <v>128438321</v>
       </c>
       <c r="B7" t="n">
-        <v>78695</v>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586673</v>
+        <v>586605</v>
       </c>
       <c r="R7" t="n">
-        <v>7089842</v>
+        <v>7090026</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1289,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128440016</v>
+        <v>128439094</v>
       </c>
       <c r="B8" t="n">
-        <v>78695</v>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1324,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586691</v>
+        <v>586622</v>
       </c>
       <c r="R8" t="n">
-        <v>7089809</v>
+        <v>7089926</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1386,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128437589</v>
+        <v>128439819</v>
       </c>
       <c r="B9" t="n">
-        <v>91676</v>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586739</v>
+        <v>586673</v>
       </c>
       <c r="R9" t="n">
-        <v>7089865</v>
+        <v>7089842</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1483,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128440115</v>
+        <v>128440016</v>
       </c>
       <c r="B10" t="n">
-        <v>92805</v>
+        <v>78993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586688</v>
+        <v>586691</v>
       </c>
       <c r="R10" t="n">
-        <v>7089811</v>
+        <v>7089809</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1580,48 +1548,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128438132</v>
+        <v>75247200</v>
       </c>
       <c r="B11" t="n">
-        <v>90547</v>
+        <v>92083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+          <t>Nybäcksberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586666</v>
+        <v>586572</v>
       </c>
       <c r="R11" t="n">
-        <v>7089955</v>
+        <v>7089895</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1645,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2018-07-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2018-07-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1661,48 +1629,65 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>brandpåverkad tallskog på moränkulle</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal tallåga</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128441773</v>
+        <v>128437589</v>
       </c>
       <c r="B12" t="n">
-        <v>92805</v>
+        <v>92083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1712,10 +1697,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586682</v>
+        <v>586739</v>
       </c>
       <c r="R12" t="n">
-        <v>7089791</v>
+        <v>7089865</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1774,32 +1759,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128439128</v>
+        <v>128437746</v>
       </c>
       <c r="B13" t="n">
-        <v>80170</v>
+        <v>92083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>1503</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1809,10 +1794,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586657</v>
+        <v>586698</v>
       </c>
       <c r="R13" t="n">
-        <v>7089905</v>
+        <v>7089852</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1871,32 +1856,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128437871</v>
+        <v>128439054</v>
       </c>
       <c r="B14" t="n">
-        <v>78695</v>
+        <v>92083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1891,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586697</v>
+        <v>586635</v>
       </c>
       <c r="R14" t="n">
-        <v>7089867</v>
+        <v>7089949</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1968,10 +1953,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128439671</v>
+        <v>128439616</v>
       </c>
       <c r="B15" t="n">
-        <v>91676</v>
+        <v>92083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2003,10 +1988,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586664</v>
+        <v>586660</v>
       </c>
       <c r="R15" t="n">
-        <v>7089915</v>
+        <v>7089907</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2065,32 +2050,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128437499</v>
+        <v>128439671</v>
       </c>
       <c r="B16" t="n">
-        <v>92805</v>
+        <v>92083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2085,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586750</v>
+        <v>586664</v>
       </c>
       <c r="R16" t="n">
-        <v>7089835</v>
+        <v>7089915</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2162,32 +2147,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128437645</v>
+        <v>128439799</v>
       </c>
       <c r="B17" t="n">
-        <v>79648</v>
+        <v>92083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2197,10 +2182,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586746</v>
+        <v>586664</v>
       </c>
       <c r="R17" t="n">
-        <v>7089860</v>
+        <v>7089845</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2259,32 +2244,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128447261</v>
+        <v>128438132</v>
       </c>
       <c r="B18" t="n">
-        <v>92817</v>
+        <v>90932</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4366</v>
+        <v>1962</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2279,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586663</v>
+        <v>586666</v>
       </c>
       <c r="R18" t="n">
-        <v>7089829</v>
+        <v>7089955</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2356,10 +2341,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128439814</v>
+        <v>128438750</v>
       </c>
       <c r="B19" t="n">
-        <v>79648</v>
+        <v>90932</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2367,21 +2352,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2391,10 +2376,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586672</v>
+        <v>586695</v>
       </c>
       <c r="R19" t="n">
-        <v>7089837</v>
+        <v>7090015</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2453,32 +2438,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128436765</v>
+        <v>128440316</v>
       </c>
       <c r="B20" t="n">
-        <v>91480</v>
+        <v>93213</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2488,10 +2473,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586735</v>
+        <v>586677</v>
       </c>
       <c r="R20" t="n">
-        <v>7089818</v>
+        <v>7089793</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2550,10 +2535,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128439094</v>
+        <v>128438427</v>
       </c>
       <c r="B21" t="n">
-        <v>78695</v>
+        <v>91962</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2561,21 +2546,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2585,10 +2570,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586622</v>
+        <v>586613</v>
       </c>
       <c r="R21" t="n">
-        <v>7089926</v>
+        <v>7090038</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2647,10 +2632,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128438427</v>
+        <v>128438577</v>
       </c>
       <c r="B22" t="n">
-        <v>93000</v>
+        <v>91962</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2682,10 +2667,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586613</v>
+        <v>586648</v>
       </c>
       <c r="R22" t="n">
-        <v>7090038</v>
+        <v>7090055</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2744,10 +2729,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128440316</v>
+        <v>128439704</v>
       </c>
       <c r="B23" t="n">
-        <v>92821</v>
+        <v>91962</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2755,21 +2740,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2059</v>
+        <v>2079</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2779,10 +2764,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586677</v>
+        <v>586666</v>
       </c>
       <c r="R23" t="n">
-        <v>7089793</v>
+        <v>7089914</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2841,10 +2826,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128437989</v>
+        <v>128436169</v>
       </c>
       <c r="B24" t="n">
-        <v>80134</v>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2852,21 +2837,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2876,10 +2861,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586701</v>
+        <v>586711</v>
       </c>
       <c r="R24" t="n">
-        <v>7089891</v>
+        <v>7089755</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2938,14 +2923,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128438055</v>
+        <v>128437168</v>
       </c>
       <c r="B25" t="n">
-        <v>92805</v>
+        <v>93197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2973,10 +2958,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586682</v>
+        <v>586767</v>
       </c>
       <c r="R25" t="n">
-        <v>7089917</v>
+        <v>7089796</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3035,10 +3020,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128438141</v>
+        <v>128437431</v>
       </c>
       <c r="B26" t="n">
-        <v>80134</v>
+        <v>93197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3046,21 +3031,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3070,10 +3055,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586666</v>
+        <v>586768</v>
       </c>
       <c r="R26" t="n">
-        <v>7089955</v>
+        <v>7089814</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3132,10 +3117,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128437686</v>
+        <v>128437499</v>
       </c>
       <c r="B27" t="n">
-        <v>79648</v>
+        <v>93197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3143,21 +3128,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3167,10 +3152,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586741</v>
+        <v>586750</v>
       </c>
       <c r="R27" t="n">
-        <v>7089870</v>
+        <v>7089835</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3229,14 +3214,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128443168</v>
+        <v>128438055</v>
       </c>
       <c r="B28" t="n">
-        <v>92805</v>
+        <v>93197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3264,10 +3249,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586666</v>
+        <v>586682</v>
       </c>
       <c r="R28" t="n">
-        <v>7089771</v>
+        <v>7089917</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3326,10 +3311,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128439751</v>
+        <v>128438499</v>
       </c>
       <c r="B29" t="n">
-        <v>79648</v>
+        <v>93197</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3337,21 +3322,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3361,10 +3346,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586681</v>
+        <v>586629</v>
       </c>
       <c r="R29" t="n">
-        <v>7089872</v>
+        <v>7090061</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3423,10 +3408,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128436152</v>
+        <v>128438643</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>93197</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3434,21 +3419,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3458,10 +3443,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>586699</v>
+        <v>586680</v>
       </c>
       <c r="R30" t="n">
-        <v>7089749</v>
+        <v>7090052</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3520,32 +3505,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128438005</v>
+        <v>128440115</v>
       </c>
       <c r="B31" t="n">
-        <v>80163</v>
+        <v>93197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3555,10 +3540,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586717</v>
+        <v>586688</v>
       </c>
       <c r="R31" t="n">
-        <v>7089885</v>
+        <v>7089811</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3617,10 +3602,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128436148</v>
+        <v>128441773</v>
       </c>
       <c r="B32" t="n">
-        <v>79648</v>
+        <v>93197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3628,21 +3613,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3652,10 +3637,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586698</v>
+        <v>586682</v>
       </c>
       <c r="R32" t="n">
-        <v>7089750</v>
+        <v>7089791</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3714,32 +3699,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128439799</v>
+        <v>128443168</v>
       </c>
       <c r="B33" t="n">
-        <v>91676</v>
+        <v>93197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3749,10 +3734,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586664</v>
+        <v>586666</v>
       </c>
       <c r="R33" t="n">
-        <v>7089845</v>
+        <v>7089771</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3811,10 +3796,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128439616</v>
+        <v>128437925</v>
       </c>
       <c r="B34" t="n">
-        <v>91676</v>
+        <v>93201</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3822,21 +3807,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1503</v>
+        <v>4365</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3846,10 +3831,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586660</v>
+        <v>586697</v>
       </c>
       <c r="R34" t="n">
-        <v>7089907</v>
+        <v>7089867</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3908,32 +3893,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128437925</v>
+        <v>128447261</v>
       </c>
       <c r="B35" t="n">
-        <v>92809</v>
+        <v>93209</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3943,10 +3928,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586697</v>
+        <v>586663</v>
       </c>
       <c r="R35" t="n">
-        <v>7089867</v>
+        <v>7089829</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4005,32 +3990,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128436482</v>
+        <v>128436765</v>
       </c>
       <c r="B36" t="n">
-        <v>78786</v>
+        <v>91872</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4040,10 +4025,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586745</v>
+        <v>586735</v>
       </c>
       <c r="R36" t="n">
-        <v>7089805</v>
+        <v>7089818</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4102,32 +4087,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128438053</v>
+        <v>128437171</v>
       </c>
       <c r="B37" t="n">
-        <v>78786</v>
+        <v>91872</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4137,10 +4122,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586682</v>
+        <v>586767</v>
       </c>
       <c r="R37" t="n">
-        <v>7089916</v>
+        <v>7089796</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4199,10 +4184,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128436799</v>
+        <v>128436111</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>93223</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4210,34 +4195,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5448</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Nybäcksberget, Nybäcksberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586743</v>
+        <v>586697</v>
       </c>
       <c r="R38" t="n">
-        <v>7089814</v>
+        <v>7089757</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4278,6 +4266,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4296,10 +4285,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128436295</v>
+        <v>128437355</v>
       </c>
       <c r="B39" t="n">
-        <v>78695</v>
+        <v>93223</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4307,21 +4296,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>5448</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4331,10 +4320,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586729</v>
+        <v>586759</v>
       </c>
       <c r="R39" t="n">
-        <v>7089765</v>
+        <v>7089808</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4393,10 +4382,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128437746</v>
+        <v>128436152</v>
       </c>
       <c r="B40" t="n">
-        <v>91676</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4404,21 +4393,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4428,10 +4417,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586698</v>
+        <v>586699</v>
       </c>
       <c r="R40" t="n">
-        <v>7089852</v>
+        <v>7089749</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4490,32 +4479,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128437630</v>
+        <v>128436799</v>
       </c>
       <c r="B41" t="n">
-        <v>78786</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4525,10 +4514,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586750</v>
+        <v>586743</v>
       </c>
       <c r="R41" t="n">
-        <v>7089861</v>
+        <v>7089814</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4587,32 +4576,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128446039</v>
+        <v>128437765</v>
       </c>
       <c r="B42" t="n">
-        <v>78037</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4611,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586654</v>
+        <v>586703</v>
       </c>
       <c r="R42" t="n">
-        <v>7089830</v>
+        <v>7089847</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4684,32 +4673,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128439054</v>
+        <v>128436482</v>
       </c>
       <c r="B43" t="n">
-        <v>91676</v>
+        <v>79084</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4719,10 +4708,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586635</v>
+        <v>586745</v>
       </c>
       <c r="R43" t="n">
-        <v>7089949</v>
+        <v>7089805</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4781,32 +4770,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128439342</v>
+        <v>128436636</v>
       </c>
       <c r="B44" t="n">
-        <v>91776</v>
+        <v>79084</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>65</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4816,10 +4805,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586657</v>
+        <v>586763</v>
       </c>
       <c r="R44" t="n">
-        <v>7089895</v>
+        <v>7089805</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4878,10 +4867,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128439704</v>
+        <v>128437387</v>
       </c>
       <c r="B45" t="n">
-        <v>93000</v>
+        <v>79084</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4889,21 +4878,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4913,10 +4902,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586666</v>
+        <v>586758</v>
       </c>
       <c r="R45" t="n">
-        <v>7089914</v>
+        <v>7089808</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -4975,10 +4964,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128439117</v>
+        <v>128437630</v>
       </c>
       <c r="B46" t="n">
-        <v>80134</v>
+        <v>79084</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4986,21 +4975,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5010,10 +4999,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586650</v>
+        <v>586750</v>
       </c>
       <c r="R46" t="n">
-        <v>7089902</v>
+        <v>7089861</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5072,10 +5061,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128437765</v>
+        <v>128437669</v>
       </c>
       <c r="B47" t="n">
-        <v>79029</v>
+        <v>79084</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5083,21 +5072,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5107,10 +5096,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586703</v>
+        <v>586742</v>
       </c>
       <c r="R47" t="n">
-        <v>7089847</v>
+        <v>7089870</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5169,10 +5158,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128436111</v>
+        <v>128438053</v>
       </c>
       <c r="B48" t="n">
-        <v>92832</v>
+        <v>79084</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5180,37 +5169,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5448</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Nybäcksberget, Nybäcksberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>586697</v>
+        <v>586682</v>
       </c>
       <c r="R48" t="n">
-        <v>7089757</v>
+        <v>7089916</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5251,7 +5237,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5267,6 +5252,1592 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128439941</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>586701</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7089852</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128436148</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>586698</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7089750</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128437645</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>586746</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7089860</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128437686</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>586741</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7089870</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128439751</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>586681</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7089872</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128439814</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>586672</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7089837</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128437989</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>586701</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7089891</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128438141</v>
+      </c>
+      <c r="B56" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>586666</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7089955</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128438180</v>
+      </c>
+      <c r="B57" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>586656</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7090016</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128438807</v>
+      </c>
+      <c r="B58" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>586701</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7090019</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128439117</v>
+      </c>
+      <c r="B59" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>586650</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7089902</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128438005</v>
+      </c>
+      <c r="B60" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>586717</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7089885</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128439128</v>
+      </c>
+      <c r="B61" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>586657</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7089905</v>
+      </c>
+      <c r="S61" t="n">
+        <v>15</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128446039</v>
+      </c>
+      <c r="B62" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>586654</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7089830</v>
+      </c>
+      <c r="S62" t="n">
+        <v>15</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>75247197</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>586735</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7089941</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2018-07-28</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2018-07-28</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>sydvänd, brandpräglad gammal tallskog</t>
+        </is>
+      </c>
+      <c r="AN63" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>2 substratenheter # tallhögstubbar med brandspår</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>75247198</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>586735</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7089941</v>
+      </c>
+      <c r="S64" t="n">
+        <v>25</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2018-07-28</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2018-07-28</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>sydvänd, brandpräglad gammal tallskog</t>
+        </is>
+      </c>
+      <c r="AN64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>2 substratenheter # tallhögstubbar med brandspår</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38268-2025 artfynd.xlsx
+++ b/artfynd/A 38268-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AZ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128439342</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128436295</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128436683</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128437417</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128437871</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128438321</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128439094</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128439819</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128440016</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1659,6 +1709,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75247200</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1756,6 +1811,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128437589</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1853,6 +1913,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128437746</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1950,6 +2015,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128439054</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2047,6 +2117,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128439616</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2144,6 +2219,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128439671</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2241,6 +2321,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128439799</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2338,6 +2423,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128438132</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2435,6 +2525,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128438750</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2532,6 +2627,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128440316</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2629,6 +2729,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128438427</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2726,6 +2831,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128438577</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2823,6 +2933,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128439704</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2920,6 +3035,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128436169</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3017,6 +3137,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128437168</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3114,6 +3239,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128437431</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3211,6 +3341,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128437499</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3308,6 +3443,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128438055</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3405,6 +3545,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128438499</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3502,6 +3647,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128438643</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3599,6 +3749,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128440115</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3696,6 +3851,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128441773</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3793,6 +3953,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128443168</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3890,6 +4055,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128437925</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3987,6 +4157,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128447261</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4084,6 +4259,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128436765</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4181,6 +4361,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128437171</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4282,6 +4467,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128436111</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4379,6 +4569,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128437355</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4476,6 +4671,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128436152</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4573,6 +4773,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128436799</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4670,6 +4875,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128437765</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4767,6 +4977,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128436482</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4864,6 +5079,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128436636</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4961,6 +5181,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128437387</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5058,6 +5283,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128437630</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5155,6 +5385,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128437669</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5252,6 +5487,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128438053</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5349,6 +5589,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128439941</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5446,6 +5691,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128436148</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5543,6 +5793,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128437645</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5640,6 +5895,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128437686</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5737,6 +5997,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128439751</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5834,6 +6099,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128439814</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5931,6 +6201,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128437989</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6028,6 +6303,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128438141</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6125,6 +6405,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128438180</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6222,6 +6507,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128438807</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6319,6 +6609,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128439117</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6416,6 +6711,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128438005</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6513,6 +6813,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128439128</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6610,6 +6915,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128446039</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6724,6 +7034,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75247197</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6838,8 +7153,78 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75247198</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>